--- a/src/pages/data/data_corp_demo.xlsx
+++ b/src/pages/data/data_corp_demo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/corporate_project/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF7051B1-0EFF-45E5-BDCF-3F6080ED43BA}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06E9645C-BC73-406C-A4F7-12130B7B560F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11040" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_corp" sheetId="1" r:id="rId1"/>
@@ -23,17 +23,28 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_corp!$A$1:$H$229</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="40">
   <si>
     <t>UNIDAD_ACADEMICA</t>
   </si>
@@ -168,12 +179,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -188,11 +205,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7343,14 +7361,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{482657F8-43FC-45F9-9834-57F8F380F1AB}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7457,342 +7475,427 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7">
-        <v>141</v>
-      </c>
-      <c r="D7">
-        <v>87</v>
-      </c>
-      <c r="E7">
-        <v>0.61702127659574468</v>
+        <v>7</v>
+      </c>
+      <c r="C7" s="2">
+        <v>163</v>
+      </c>
+      <c r="D7" s="2">
+        <v>65</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.4</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="D8">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="E8">
-        <v>0.51724137931034486</v>
+        <v>0.61702127659574468</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
       </c>
       <c r="C9">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D9">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="E9">
-        <v>0.6484375</v>
+        <v>0.51724137931034486</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B10" t="s">
         <v>18</v>
       </c>
       <c r="C10">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D10">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="E10">
-        <v>0.5892857142857143</v>
+        <v>0.6484375</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
       <c r="C11">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="D11">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E11">
-        <v>0.6</v>
+        <v>0.5892857142857143</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c r="D12">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="E12">
-        <v>0.54802259887005644</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13">
-        <v>149</v>
-      </c>
-      <c r="D13">
-        <v>85</v>
-      </c>
-      <c r="E13">
-        <v>0.57046979865771807</v>
+        <v>18</v>
+      </c>
+      <c r="C13" s="2">
+        <v>124</v>
+      </c>
+      <c r="D13" s="2">
+        <v>74</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.6</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
       </c>
       <c r="C14">
-        <v>115</v>
+        <v>177</v>
       </c>
       <c r="D14">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="E14">
-        <v>0.59130434782608698</v>
+        <v>0.54802259887005644</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B15" t="s">
         <v>19</v>
       </c>
       <c r="C15">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="D15">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="E15">
-        <v>0.61206896551724133</v>
+        <v>0.57046979865771807</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
       </c>
       <c r="C16">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="D16">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16">
-        <v>0.4861111111111111</v>
+        <v>0.59130434782608698</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
-        <v>540</v>
+        <v>116</v>
       </c>
       <c r="D17">
-        <v>250</v>
+        <v>71</v>
       </c>
       <c r="E17">
-        <v>0.46296296296296297</v>
+        <v>0.61206896551724133</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18">
-        <v>395</v>
+        <v>144</v>
       </c>
       <c r="D18">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="E18">
-        <v>0.43037974683544306</v>
+        <v>0.4861111111111111</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19">
-        <v>502</v>
-      </c>
-      <c r="D19">
-        <v>247</v>
-      </c>
-      <c r="E19">
-        <v>0.49203187250996017</v>
+        <v>19</v>
+      </c>
+      <c r="C19" s="2">
+        <v>137</v>
+      </c>
+      <c r="D19" s="2">
+        <v>75</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B20" t="s">
         <v>20</v>
       </c>
       <c r="C20">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="D20">
-        <v>281</v>
+        <v>250</v>
       </c>
       <c r="E20">
-        <v>0.51277372262773724</v>
+        <v>0.46296296296296297</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B21" t="s">
         <v>20</v>
       </c>
       <c r="C21">
-        <v>659</v>
+        <v>395</v>
       </c>
       <c r="D21">
-        <v>342</v>
+        <v>170</v>
       </c>
       <c r="E21">
-        <v>0.51896813353566007</v>
+        <v>0.43037974683544306</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C22">
-        <v>303</v>
+        <v>502</v>
       </c>
       <c r="D22">
-        <v>124</v>
+        <v>247</v>
       </c>
       <c r="E22">
-        <v>0.40924092409240925</v>
+        <v>0.49203187250996017</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C23">
-        <v>263</v>
+        <v>548</v>
       </c>
       <c r="D23">
-        <v>117</v>
+        <v>281</v>
       </c>
       <c r="E23">
-        <v>0.44486692015209123</v>
+        <v>0.51277372262773724</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C24">
-        <v>260</v>
+        <v>659</v>
       </c>
       <c r="D24">
-        <v>101</v>
+        <v>342</v>
       </c>
       <c r="E24">
-        <v>0.38846153846153847</v>
+        <v>0.51896813353566007</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25">
-        <v>263</v>
-      </c>
-      <c r="D25">
-        <v>100</v>
-      </c>
-      <c r="E25">
-        <v>0.38022813688212925</v>
+        <v>20</v>
+      </c>
+      <c r="C25" s="2">
+        <v>742</v>
+      </c>
+      <c r="D25" s="2">
+        <v>378</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0.51</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B26" t="s">
         <v>25</v>
       </c>
       <c r="C26">
+        <v>303</v>
+      </c>
+      <c r="D26">
+        <v>124</v>
+      </c>
+      <c r="E26">
+        <v>0.40924092409240925</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2022</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27">
+        <v>263</v>
+      </c>
+      <c r="D27">
+        <v>117</v>
+      </c>
+      <c r="E27">
+        <v>0.44486692015209123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2023</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28">
+        <v>260</v>
+      </c>
+      <c r="D28">
+        <v>101</v>
+      </c>
+      <c r="E28">
+        <v>0.38846153846153847</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2024</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29">
+        <v>263</v>
+      </c>
+      <c r="D29">
+        <v>100</v>
+      </c>
+      <c r="E29">
+        <v>0.38022813688212925</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2025</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30">
         <v>297</v>
       </c>
-      <c r="D26">
+      <c r="D30">
         <v>141</v>
       </c>
-      <c r="E26">
+      <c r="E30">
         <v>0.47474747474747475</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2026</v>
+      </c>
+      <c r="B31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="2">
+        <v>306</v>
+      </c>
+      <c r="D31" s="2">
+        <v>129</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>

--- a/src/pages/data/data_corp_demo.xlsx
+++ b/src/pages/data/data_corp_demo.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/corporate_project/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06E9645C-BC73-406C-A4F7-12130B7B560F}"/>
+  <xr:revisionPtr revIDLastSave="178" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBFF0763-671A-4E02-B2FF-3537CD8A5363}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11040" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="779" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_corp" sheetId="1" r:id="rId1"/>
     <sheet name="data_demo" sheetId="2" r:id="rId2"/>
     <sheet name="data_mercado_media" sheetId="3" r:id="rId3"/>
-    <sheet name="data_mercado_basica" sheetId="4" r:id="rId4"/>
-    <sheet name="data_mercado_corp" sheetId="5" r:id="rId5"/>
-    <sheet name="data_sae_corp" sheetId="6" r:id="rId6"/>
+    <sheet name="data_mercado_media_col" sheetId="8" r:id="rId4"/>
+    <sheet name="data_mercado_basica" sheetId="4" r:id="rId5"/>
+    <sheet name="data_mercado_bas_col" sheetId="7" r:id="rId6"/>
+    <sheet name="data_mercado_corp" sheetId="5" r:id="rId7"/>
+    <sheet name="data_sae_corp" sheetId="6" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_corp!$A$1:$H$229</definedName>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="108">
   <si>
     <t>UNIDAD_ACADEMICA</t>
   </si>
@@ -164,6 +166,210 @@
   </si>
   <si>
     <t>% ADMITIDOS</t>
+  </si>
+  <si>
+    <t>COLEGIO ALCAZAR</t>
+  </si>
+  <si>
+    <t>COLEGIO ALTA CUMBRE</t>
+  </si>
+  <si>
+    <t>COLEGIO MARIA AUXILIADORA</t>
+  </si>
+  <si>
+    <t>COLEGIO PARTICULAR CLAUDIO GAY</t>
+  </si>
+  <si>
+    <t>COLEGIO SAN SEBASTIAN</t>
+  </si>
+  <si>
+    <t>ESCUELA BASICA GRAL.JOSE MIGUEL CARRERA</t>
+  </si>
+  <si>
+    <t>ESCUELA BASICA RIO BLANCO</t>
+  </si>
+  <si>
+    <t>ESCUELA EL SAUCE</t>
+  </si>
+  <si>
+    <t>ESCUELA ESPANA</t>
+  </si>
+  <si>
+    <t>ESCUELA FERROVIARIA</t>
+  </si>
+  <si>
+    <t>ESCUELA GABRIELA MISTRAL</t>
+  </si>
+  <si>
+    <t>ESCUELA IGNACIO CARRERA PINTO</t>
+  </si>
+  <si>
+    <t>ESCUELA JOHN KENNEDY</t>
+  </si>
+  <si>
+    <t>ESCUELA PARTICULAR HUMBERTO CASARINO</t>
+  </si>
+  <si>
+    <t>ESCUELA PARTICULAR JEAN PIAGET</t>
+  </si>
+  <si>
+    <t>ESCUELA PARTICULAR N°27 EDÉN DEL NIÑO</t>
+  </si>
+  <si>
+    <t>ESCUELA PARTICULAR SAN JOSE</t>
+  </si>
+  <si>
+    <t>LICEO MAXIMILIANO SALAS MARCHAN</t>
+  </si>
+  <si>
+    <t>LICEO REPUBLICA ARGENTINA</t>
+  </si>
+  <si>
+    <t>LICEO SANTA CLARA</t>
+  </si>
+  <si>
+    <t>COLEGIO ALONSO DE ERCILLA</t>
+  </si>
+  <si>
+    <t>COLEGIO GREENLAND SAN FELIPE</t>
+  </si>
+  <si>
+    <t>COLEGIO JOSE AGUSTIN GOMEZ</t>
+  </si>
+  <si>
+    <t>COLEGIO PARTICULAR PUMANQUE</t>
+  </si>
+  <si>
+    <t>COLEGIO PIRAMIDE</t>
+  </si>
+  <si>
+    <t>COLEGIO SAN PABLO</t>
+  </si>
+  <si>
+    <t>COLEGIO SANTA JUANA DE ARCO</t>
+  </si>
+  <si>
+    <t>COLEGIO VEDRUNA</t>
+  </si>
+  <si>
+    <t>ESCUELA 21 DE MAYO</t>
+  </si>
+  <si>
+    <t>ESCUELA ALMENDRAL</t>
+  </si>
+  <si>
+    <t>ESCUELA BASICA BERNARDO O HIGGINS R.</t>
+  </si>
+  <si>
+    <t>ESCUELA BASICA CAROLINA OCAMPO GARCIA</t>
+  </si>
+  <si>
+    <t>ESCUELA BASICA JOSE DE SAN MARTIN</t>
+  </si>
+  <si>
+    <t>ESCUELA BUCALEMITO</t>
+  </si>
+  <si>
+    <t>ESCUELA BUEN PASTOR</t>
+  </si>
+  <si>
+    <t>ESCUELA CARMELA CARVAJAL DE PRAT</t>
+  </si>
+  <si>
+    <t>ESCUELA HERIBERTO BERMUDEZ CRUZ</t>
+  </si>
+  <si>
+    <t>ESCUELA HOSPITALARIA SAN CAMILO</t>
+  </si>
+  <si>
+    <t>ESCUELA JOHN F KENNEDY</t>
+  </si>
+  <si>
+    <t>ESCUELA JOSÉ ANTONIO MANSO DE VELASCO</t>
+  </si>
+  <si>
+    <t>ESCUELA JOSE BERNARDO SUAREZ</t>
+  </si>
+  <si>
+    <t>ESCUELA JUAN GOMEZ MILLAS</t>
+  </si>
+  <si>
+    <t>ESCUELA MANUEL RODRIGUEZ ERDOIZA</t>
+  </si>
+  <si>
+    <t>ESCUELA MATEO COKLJAT K</t>
+  </si>
+  <si>
+    <t>ESCUELA REPUBLICA ARGENTINA</t>
+  </si>
+  <si>
+    <t>ESCUELA SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>LICEO BICENTENARIO CORDILLERA DE SAN FELIPE</t>
+  </si>
+  <si>
+    <t>LICEO BICENTENARIO CORINA URBINA VILLANUEVA</t>
+  </si>
+  <si>
+    <t>LICEO DOCTOR ROBERTO HUMERES O.</t>
+  </si>
+  <si>
+    <t>LICEO SAN FELIPE</t>
+  </si>
+  <si>
+    <t>SUNNYLAND SCHOOL</t>
+  </si>
+  <si>
+    <t>JARDIN INFANTIL REMOLINO</t>
+  </si>
+  <si>
+    <t>COLEGIOS GRUPO DE REFERENCIA</t>
+  </si>
+  <si>
+    <t>COLEGIOS GRUPO DE REFERENCIA TP</t>
+  </si>
+  <si>
+    <t>COLEGIOS GRUPO DE REFERENCIA HC</t>
+  </si>
+  <si>
+    <t>INSTITUTO AGRICOLA PASCUAL BABURIZZA</t>
+  </si>
+  <si>
+    <t>LICEO BICENTENARIO TÉCNICO AMANCAY</t>
+  </si>
+  <si>
+    <t>LICEO COMERCIAL DE LOS ANDES</t>
+  </si>
+  <si>
+    <t>LICEO POLITECNICO AMERICA</t>
+  </si>
+  <si>
+    <t>LICEO SAN ESTEBAN</t>
+  </si>
+  <si>
+    <t>LICEO PARROQUIAL TERESITA DE LOS ANDES</t>
+  </si>
+  <si>
+    <t>LICEO TEC.PROFESIONAL PEDRO AGUIRRE CERDA</t>
+  </si>
+  <si>
+    <t>COLEGIO ASSUNTA PALLOTA</t>
+  </si>
+  <si>
+    <t>COLEGIO BICENTENARIO SANTA MARÍA DE ACONCAGUA</t>
+  </si>
+  <si>
+    <t>ESCUELA AGRICOLA DE SAN FELIPE</t>
+  </si>
+  <si>
+    <t>LICEO BICENTENARIO GUILLERMO RICHARDS CUEVAS</t>
+  </si>
+  <si>
+    <t>LICEO DARIO SALAS</t>
+  </si>
+  <si>
+    <t>LICEO MANUEL MARIN</t>
   </si>
 </sst>
 </file>
@@ -1715,19 +1921,19 @@
         <v>8</v>
       </c>
       <c r="D47">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G47">
         <v>40</v>
       </c>
       <c r="H47">
-        <v>0.9</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -1747,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G48">
         <v>58</v>
@@ -1773,7 +1979,7 @@
         <v>4</v>
       </c>
       <c r="F49">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G49">
         <v>33</v>
@@ -1793,19 +1999,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E50">
         <v>3</v>
       </c>
       <c r="F50">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G50">
         <v>88</v>
       </c>
       <c r="H50">
-        <v>0.92045454545454597</v>
+        <v>0.88636363636363602</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -1819,19 +2025,19 @@
         <v>11</v>
       </c>
       <c r="D51">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E51">
         <v>1</v>
       </c>
       <c r="F51">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G51">
         <v>63</v>
       </c>
       <c r="H51">
-        <v>0.84126984126984095</v>
+        <v>0.82539682539682502</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -1845,7 +2051,7 @@
         <v>14</v>
       </c>
       <c r="D52">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1857,7 +2063,7 @@
         <v>102</v>
       </c>
       <c r="H52">
-        <v>0.89215686274509798</v>
+        <v>0.87254901960784303</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -1871,19 +2077,19 @@
         <v>13</v>
       </c>
       <c r="D53">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E53">
         <v>2</v>
       </c>
       <c r="F53">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G53">
         <v>72</v>
       </c>
       <c r="H53">
-        <v>0.94444444444444398</v>
+        <v>0.93055555555555602</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -1929,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="F55">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G55">
         <v>30</v>
@@ -2085,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="F61">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -2125,25 +2331,25 @@
         <v>18</v>
       </c>
       <c r="B63">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C63" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D63">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F63">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G63">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="H63">
-        <v>0.88235294117647101</v>
+        <v>0.84210526315789502</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -2151,25 +2357,25 @@
         <v>18</v>
       </c>
       <c r="B64">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="C64" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D64">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="E64">
         <v>2</v>
       </c>
       <c r="F64">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G64">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H64">
-        <v>0.86363636363636398</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -2177,25 +2383,25 @@
         <v>18</v>
       </c>
       <c r="B65">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="C65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D65">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G65">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="H65">
-        <v>0.89552238805970197</v>
+        <v>0.86046511627906996</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -2203,25 +2409,25 @@
         <v>18</v>
       </c>
       <c r="B66">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="C66" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D66">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G66">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="H66">
-        <v>0.89873417721519</v>
+        <v>0.82352941176470595</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -2229,25 +2435,25 @@
         <v>18</v>
       </c>
       <c r="B67">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="C67" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D67">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E67">
         <v>0</v>
       </c>
       <c r="F67">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G67">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="H67">
-        <v>0.86842105263157898</v>
+        <v>0.83636363636363598</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -2258,22 +2464,22 @@
         <v>2021</v>
       </c>
       <c r="C68" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D68">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F68">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G68">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="H68">
-        <v>0.79591836734693899</v>
+        <v>0.86363636363636398</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -2281,25 +2487,25 @@
         <v>18</v>
       </c>
       <c r="B69">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C69" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D69">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G69">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H69">
-        <v>0.96385542168674698</v>
+        <v>0.70370370370370405</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -2307,25 +2513,25 @@
         <v>18</v>
       </c>
       <c r="B70">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="C70" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D70">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="E70">
         <v>0</v>
       </c>
       <c r="F70">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G70">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="H70">
-        <v>0.91011235955056202</v>
+        <v>0.811594202898551</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -2333,25 +2539,25 @@
         <v>18</v>
       </c>
       <c r="B71">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C71" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D71">
         <v>40</v>
       </c>
       <c r="E71">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G71">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H71">
-        <v>0.84210526315789502</v>
+        <v>0.677966101694915</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -2359,25 +2565,25 @@
         <v>18</v>
       </c>
       <c r="B72">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D72">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F72">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G72">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="H72">
-        <v>0.85882352941176499</v>
+        <v>0.91228070175438603</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -2385,25 +2591,25 @@
         <v>18</v>
       </c>
       <c r="B73">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="C73" t="s">
         <v>10</v>
       </c>
       <c r="D73">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G73">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="H73">
-        <v>0.70370370370370405</v>
+        <v>0.94736842105263197</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -2411,25 +2617,25 @@
         <v>18</v>
       </c>
       <c r="B74">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C74" t="s">
         <v>9</v>
       </c>
       <c r="D74">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G74">
         <v>67</v>
       </c>
       <c r="H74">
-        <v>0.77611940298507498</v>
+        <v>0.89552238805970197</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -2440,22 +2646,22 @@
         <v>2022</v>
       </c>
       <c r="C75" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D75">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G75">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="H75">
-        <v>0.85555555555555596</v>
+        <v>0.77611940298507498</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -2463,25 +2669,25 @@
         <v>18</v>
       </c>
       <c r="B76">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C76" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76">
+        <v>58</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
         <v>11</v>
       </c>
-      <c r="D76">
-        <v>60</v>
-      </c>
-      <c r="E76">
-        <v>1</v>
-      </c>
-      <c r="F76">
-        <v>12</v>
-      </c>
       <c r="G76">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H76">
-        <v>0.82432432432432401</v>
+        <v>0.80555555555555602</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -2489,25 +2695,25 @@
         <v>18</v>
       </c>
       <c r="B77">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C77" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D77">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F77">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G77">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H77">
-        <v>0.772151898734177</v>
+        <v>0.79729729729729704</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -2515,25 +2721,25 @@
         <v>18</v>
       </c>
       <c r="B78">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D78">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="E78">
         <v>0</v>
       </c>
       <c r="F78">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G78">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="H78">
-        <v>0.82222222222222197</v>
+        <v>0.82142857142857095</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -2541,25 +2747,25 @@
         <v>18</v>
       </c>
       <c r="B79">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="C79" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D79">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G79">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="H79">
-        <v>0.76190476190476197</v>
+        <v>0.80952380952380998</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -2567,25 +2773,25 @@
         <v>18</v>
       </c>
       <c r="B80">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C80" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D80">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E80">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F80">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G80">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="H80">
-        <v>0.86</v>
+        <v>0.86842105263157898</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -2593,25 +2799,25 @@
         <v>18</v>
       </c>
       <c r="B81">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C81" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D81">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81">
         <v>12</v>
       </c>
       <c r="G81">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="H81">
-        <v>0.87640449438202195</v>
+        <v>0.82432432432432401</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -2622,22 +2828,22 @@
         <v>2023</v>
       </c>
       <c r="C82" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D82">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G82">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H82">
-        <v>0.811594202898551</v>
+        <v>0.86153846153846203</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -2645,25 +2851,25 @@
         <v>18</v>
       </c>
       <c r="B83">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C83" t="s">
         <v>11</v>
       </c>
       <c r="D83">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G83">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H83">
-        <v>0.86153846153846203</v>
+        <v>0.82608695652173902</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -2671,25 +2877,25 @@
         <v>18</v>
       </c>
       <c r="B84">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C84" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D84">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G84">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H84">
-        <v>0.80555555555555602</v>
+        <v>0.86486486486486502</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -2697,25 +2903,25 @@
         <v>18</v>
       </c>
       <c r="B85">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="C85" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D85">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F85">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G85">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="H85">
-        <v>0.85555555555555596</v>
+        <v>0.93442622950819698</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -2723,25 +2929,25 @@
         <v>18</v>
       </c>
       <c r="B86">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C86" t="s">
         <v>13</v>
       </c>
       <c r="D86">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="E86">
         <v>1</v>
       </c>
       <c r="F86">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G86">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H86">
-        <v>0.80821917808219201</v>
+        <v>0.96385542168674698</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -2749,25 +2955,25 @@
         <v>18</v>
       </c>
       <c r="B87">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C87" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D87">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E87">
         <v>0</v>
       </c>
       <c r="F87">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G87">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H87">
-        <v>0.68918918918918903</v>
+        <v>0.772151898734177</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -2778,22 +2984,22 @@
         <v>2023</v>
       </c>
       <c r="C88" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D88">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="E88">
         <v>1</v>
       </c>
       <c r="F88">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G88">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="H88">
-        <v>0.88235294117647101</v>
+        <v>0.80821917808219201</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -2804,22 +3010,22 @@
         <v>2024</v>
       </c>
       <c r="C89" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D89">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F89">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G89">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="H89">
-        <v>0.86046511627906996</v>
+        <v>0.84615384615384603</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -2827,25 +3033,25 @@
         <v>18</v>
       </c>
       <c r="B90">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C90" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D90">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E90">
         <v>0</v>
       </c>
       <c r="F90">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G90">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="H90">
-        <v>0.677966101694915</v>
+        <v>0.89552238805970197</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -2853,25 +3059,25 @@
         <v>18</v>
       </c>
       <c r="B91">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C91" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D91">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F91">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G91">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H91">
-        <v>0.79729729729729704</v>
+        <v>0.88157894736842102</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -2879,25 +3085,25 @@
         <v>18</v>
       </c>
       <c r="B92">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C92" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D92">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="E92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92">
         <v>10</v>
       </c>
       <c r="G92">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="H92">
-        <v>0.82608695652173902</v>
+        <v>0.88235294117647101</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -2905,13 +3111,13 @@
         <v>18</v>
       </c>
       <c r="B93">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C93" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D93">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -2920,10 +3126,10 @@
         <v>16</v>
       </c>
       <c r="G93">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="H93">
-        <v>0.84615384615384603</v>
+        <v>0.82222222222222197</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -2931,25 +3137,25 @@
         <v>18</v>
       </c>
       <c r="B94">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C94" t="s">
         <v>14</v>
       </c>
       <c r="D94">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F94">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G94">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H94">
-        <v>0.84848484848484795</v>
+        <v>0.68918918918918903</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -2960,22 +3166,22 @@
         <v>2024</v>
       </c>
       <c r="C95" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D95">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G95">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H95">
-        <v>0.81690140845070403</v>
+        <v>0.84848484848484795</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -2983,25 +3189,25 @@
         <v>18</v>
       </c>
       <c r="B96">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C96" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D96">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E96">
         <v>0</v>
       </c>
       <c r="F96">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G96">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="H96">
-        <v>0.83333333333333404</v>
+        <v>0.84507042253521103</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -3009,25 +3215,25 @@
         <v>18</v>
       </c>
       <c r="B97">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C97" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D97">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="E97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F97">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G97">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="H97">
-        <v>0.88461538461538403</v>
+        <v>0.86904761904761896</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -3035,25 +3241,25 @@
         <v>18</v>
       </c>
       <c r="B98">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="C98" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D98">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="E98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F98">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G98">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="H98">
-        <v>0.82352941176470595</v>
+        <v>0.89873417721519</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -3061,25 +3267,25 @@
         <v>18</v>
       </c>
       <c r="B99">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="C99" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D99">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F99">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G99">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="H99">
-        <v>0.86486486486486502</v>
+        <v>0.85882352941176499</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -3087,25 +3293,25 @@
         <v>18</v>
       </c>
       <c r="B100">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C100" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D100">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E100">
         <v>2</v>
       </c>
       <c r="F100">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G100">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="H100">
-        <v>0.91228070175438603</v>
+        <v>0.85555555555555596</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -3113,25 +3319,25 @@
         <v>18</v>
       </c>
       <c r="B101">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C101" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D101">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E101">
         <v>0</v>
       </c>
       <c r="F101">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G101">
         <v>71</v>
       </c>
       <c r="H101">
-        <v>0.84507042253521103</v>
+        <v>0.81690140845070403</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -3142,22 +3348,22 @@
         <v>2025</v>
       </c>
       <c r="C102" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D102">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G102">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="H102">
-        <v>0.82142857142857095</v>
+        <v>0.85135135135135098</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -3165,25 +3371,25 @@
         <v>18</v>
       </c>
       <c r="B103">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C103" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D103">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F103">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G103">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H103">
-        <v>0.89552238805970197</v>
+        <v>0.91428571428571404</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -3191,25 +3397,25 @@
         <v>18</v>
       </c>
       <c r="B104">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="C104" t="s">
         <v>15</v>
       </c>
       <c r="D104">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F104">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G104">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H104">
-        <v>0.88372093023255804</v>
+        <v>0.91011235955056202</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -3217,25 +3423,25 @@
         <v>18</v>
       </c>
       <c r="B105">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="C105" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D105">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E105">
         <v>1</v>
       </c>
       <c r="F105">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G105">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="H105">
-        <v>0.85135135135135098</v>
+        <v>0.85555555555555596</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -3243,25 +3449,25 @@
         <v>18</v>
       </c>
       <c r="B106">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C106" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106">
+        <v>78</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
         <v>12</v>
       </c>
-      <c r="D106">
-        <v>41</v>
-      </c>
-      <c r="E106">
-        <v>0</v>
-      </c>
-      <c r="F106">
-        <v>14</v>
-      </c>
       <c r="G106">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="H106">
-        <v>0.85416666666666596</v>
+        <v>0.87640449438202195</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -3269,25 +3475,25 @@
         <v>18</v>
       </c>
       <c r="B107">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C107" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D107">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="E107">
         <v>0</v>
       </c>
       <c r="F107">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G107">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="H107">
-        <v>0.83636363636363598</v>
+        <v>0.83333333333333404</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -3295,25 +3501,25 @@
         <v>18</v>
       </c>
       <c r="B108">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C108" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D108">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G108">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="H108">
-        <v>0.89473684210526305</v>
+        <v>0.88372093023255804</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -3324,22 +3530,22 @@
         <v>2026</v>
       </c>
       <c r="C109" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D109">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="E109">
         <v>1</v>
       </c>
       <c r="F109">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="G109">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="H109">
-        <v>0.94736842105263197</v>
+        <v>0.85185185185185197</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -3347,25 +3553,25 @@
         <v>18</v>
       </c>
       <c r="B110">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="C110" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D110">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="E110">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F110">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G110">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="H110">
-        <v>0.92857142857142905</v>
+        <v>0.79591836734693899</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -3373,25 +3579,25 @@
         <v>18</v>
       </c>
       <c r="B111">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="C111" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D111">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G111">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="H111">
-        <v>0.80952380952380998</v>
+        <v>0.76190476190476197</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -3399,25 +3605,25 @@
         <v>18</v>
       </c>
       <c r="B112">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="C112" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D112">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112">
         <v>13</v>
       </c>
       <c r="G112">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="H112">
-        <v>0.95081967213114804</v>
+        <v>0.88235294117647101</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -3425,25 +3631,25 @@
         <v>18</v>
       </c>
       <c r="B113">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C113" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D113">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G113">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="H113">
-        <v>0.91666666666666596</v>
+        <v>0.88461538461538403</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -3451,25 +3657,25 @@
         <v>18</v>
       </c>
       <c r="B114">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C114" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D114">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G114">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="H114">
-        <v>0.87654320987654299</v>
+        <v>0.85416666666666596</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -3489,7 +3695,7 @@
         <v>1</v>
       </c>
       <c r="F115">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G115">
         <v>32</v>
@@ -3645,7 +3851,7 @@
         <v>0</v>
       </c>
       <c r="F121">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -4838,7 +5044,7 @@
         <v>47</v>
       </c>
       <c r="E167">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F167">
         <v>23</v>
@@ -4847,7 +5053,7 @@
         <v>54</v>
       </c>
       <c r="H167">
-        <v>0.96296296296296302</v>
+        <v>0.98148148148148195</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -4864,16 +5070,16 @@
         <v>117</v>
       </c>
       <c r="E168">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F168">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G168">
         <v>125</v>
       </c>
       <c r="H168">
-        <v>0.95199999999999996</v>
+        <v>0.94399999999999995</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -4893,7 +5099,7 @@
         <v>6</v>
       </c>
       <c r="F169">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G169">
         <v>89</v>
@@ -4913,7 +5119,7 @@
         <v>9</v>
       </c>
       <c r="D170">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E170">
         <v>3</v>
@@ -4925,7 +5131,7 @@
         <v>84</v>
       </c>
       <c r="H170">
-        <v>0.88095238095238104</v>
+        <v>0.85714285714285698</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -4939,19 +5145,19 @@
         <v>13</v>
       </c>
       <c r="D171">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E171">
         <v>2</v>
       </c>
       <c r="F171">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G171">
         <v>131</v>
       </c>
       <c r="H171">
-        <v>0.93893129770992401</v>
+        <v>0.90839694656488601</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -4965,19 +5171,19 @@
         <v>11</v>
       </c>
       <c r="D172">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E172">
         <v>1</v>
       </c>
       <c r="F172">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G172">
         <v>105</v>
       </c>
       <c r="H172">
-        <v>0.86666666666666703</v>
+        <v>0.838095238095238</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -4991,19 +5197,19 @@
         <v>16</v>
       </c>
       <c r="D173">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E173">
         <v>1</v>
       </c>
       <c r="F173">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G173">
         <v>111</v>
       </c>
       <c r="H173">
-        <v>0.891891891891892</v>
+        <v>0.855855855855856</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -5017,19 +5223,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E174">
         <v>0</v>
       </c>
       <c r="F174">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G174">
         <v>131</v>
       </c>
       <c r="H174">
-        <v>0.89312977099236601</v>
+        <v>0.88549618320610701</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
@@ -5049,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="F175">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G175">
         <v>34</v>
@@ -5205,7 +5411,7 @@
         <v>0</v>
       </c>
       <c r="F181">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G181">
         <v>0</v>
@@ -5745,19 +5951,19 @@
         <v>21</v>
       </c>
       <c r="D202">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="E202">
         <v>3</v>
       </c>
       <c r="F202">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G202">
         <v>351</v>
       </c>
       <c r="H202">
-        <v>0.84045584045584043</v>
+        <v>0.81481481481481477</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -5771,19 +5977,19 @@
         <v>22</v>
       </c>
       <c r="D203">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E203">
         <v>1</v>
       </c>
       <c r="F203">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G203">
         <v>319</v>
       </c>
       <c r="H203">
-        <v>0.89655172413793105</v>
+        <v>0.87147335423197492</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -5797,19 +6003,19 @@
         <v>23</v>
       </c>
       <c r="D204">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E204">
         <v>1</v>
       </c>
       <c r="F204">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G204">
         <v>220</v>
       </c>
       <c r="H204">
-        <v>0.95454545454545459</v>
+        <v>0.94545454545454544</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
@@ -5823,19 +6029,19 @@
         <v>24</v>
       </c>
       <c r="D205">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E205">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F205">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="G205">
         <v>184</v>
       </c>
       <c r="H205">
-        <v>0.72826086956521741</v>
+        <v>0.70652173913043481</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
@@ -6369,19 +6575,19 @@
         <v>21</v>
       </c>
       <c r="D226">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E226">
         <v>2</v>
       </c>
       <c r="F226">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G226">
         <v>208</v>
       </c>
       <c r="H226">
-        <v>0.85096153846153799</v>
+        <v>0.84134615384615397</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
@@ -6421,19 +6627,19 @@
         <v>22</v>
       </c>
       <c r="D228">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E228">
         <v>5</v>
       </c>
       <c r="F228">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G228">
         <v>218</v>
       </c>
       <c r="H228">
-        <v>0.92201834862385301</v>
+        <v>0.91284403669724801</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
@@ -6447,19 +6653,19 @@
         <v>24</v>
       </c>
       <c r="D229">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E229">
         <v>2</v>
       </c>
       <c r="F229">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G229">
         <v>142</v>
       </c>
       <c r="H229">
-        <v>0.77464788732394396</v>
+        <v>0.76760563380281699</v>
       </c>
     </row>
   </sheetData>
@@ -6715,6 +6921,256 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FBE924B-74F3-4C1F-8DC2-E3ED1C99C767}">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4E39ED-A2BA-4AF8-80FA-DB4BD0B334CE}">
   <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7247,13 +7703,1132 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3559129D-134A-4AB2-A379-E6F6068EBE81}">
+  <dimension ref="A1:B138"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>31</v>
+      </c>
+      <c r="B42" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>31</v>
+      </c>
+      <c r="B48" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>31</v>
+      </c>
+      <c r="B50" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>31</v>
+      </c>
+      <c r="B51" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>31</v>
+      </c>
+      <c r="B53" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>31</v>
+      </c>
+      <c r="B54" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>31</v>
+      </c>
+      <c r="B56" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>31</v>
+      </c>
+      <c r="B57" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>31</v>
+      </c>
+      <c r="B58" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>31</v>
+      </c>
+      <c r="B59" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>31</v>
+      </c>
+      <c r="B60" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>31</v>
+      </c>
+      <c r="B61" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>31</v>
+      </c>
+      <c r="B62" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>31</v>
+      </c>
+      <c r="B63" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>31</v>
+      </c>
+      <c r="B64" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>31</v>
+      </c>
+      <c r="B65" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>31</v>
+      </c>
+      <c r="B66" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>31</v>
+      </c>
+      <c r="B67" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>31</v>
+      </c>
+      <c r="B68" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>31</v>
+      </c>
+      <c r="B69" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>31</v>
+      </c>
+      <c r="B70" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>31</v>
+      </c>
+      <c r="B71" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>31</v>
+      </c>
+      <c r="B72" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>32</v>
+      </c>
+      <c r="B73" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>32</v>
+      </c>
+      <c r="B74" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>32</v>
+      </c>
+      <c r="B75" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>32</v>
+      </c>
+      <c r="B76" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>32</v>
+      </c>
+      <c r="B77" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>32</v>
+      </c>
+      <c r="B78" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>32</v>
+      </c>
+      <c r="B79" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>32</v>
+      </c>
+      <c r="B80" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>32</v>
+      </c>
+      <c r="B81" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>32</v>
+      </c>
+      <c r="B82" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>32</v>
+      </c>
+      <c r="B83" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>32</v>
+      </c>
+      <c r="B84" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>32</v>
+      </c>
+      <c r="B85" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>32</v>
+      </c>
+      <c r="B86" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>32</v>
+      </c>
+      <c r="B87" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>32</v>
+      </c>
+      <c r="B88" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>32</v>
+      </c>
+      <c r="B89" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>32</v>
+      </c>
+      <c r="B90" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>33</v>
+      </c>
+      <c r="B91" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>33</v>
+      </c>
+      <c r="B92" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>33</v>
+      </c>
+      <c r="B93" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>33</v>
+      </c>
+      <c r="B94" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>33</v>
+      </c>
+      <c r="B95" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>33</v>
+      </c>
+      <c r="B96" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>33</v>
+      </c>
+      <c r="B97" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>33</v>
+      </c>
+      <c r="B98" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>33</v>
+      </c>
+      <c r="B99" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>33</v>
+      </c>
+      <c r="B100" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>33</v>
+      </c>
+      <c r="B101" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>33</v>
+      </c>
+      <c r="B102" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>33</v>
+      </c>
+      <c r="B103" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>33</v>
+      </c>
+      <c r="B104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>33</v>
+      </c>
+      <c r="B105" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>33</v>
+      </c>
+      <c r="B106" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>33</v>
+      </c>
+      <c r="B107" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>33</v>
+      </c>
+      <c r="B108" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>34</v>
+      </c>
+      <c r="B109" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>34</v>
+      </c>
+      <c r="B110" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>34</v>
+      </c>
+      <c r="B111" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>34</v>
+      </c>
+      <c r="B112" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>34</v>
+      </c>
+      <c r="B113" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>34</v>
+      </c>
+      <c r="B114" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>34</v>
+      </c>
+      <c r="B115" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>34</v>
+      </c>
+      <c r="B116" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>34</v>
+      </c>
+      <c r="B117" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>34</v>
+      </c>
+      <c r="B118" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>34</v>
+      </c>
+      <c r="B119" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>34</v>
+      </c>
+      <c r="B120" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>34</v>
+      </c>
+      <c r="B121" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>34</v>
+      </c>
+      <c r="B122" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>34</v>
+      </c>
+      <c r="B123" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>34</v>
+      </c>
+      <c r="B124" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>34</v>
+      </c>
+      <c r="B125" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>34</v>
+      </c>
+      <c r="B126" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>34</v>
+      </c>
+      <c r="B127" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>34</v>
+      </c>
+      <c r="B128" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>34</v>
+      </c>
+      <c r="B129" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>34</v>
+      </c>
+      <c r="B130" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>34</v>
+      </c>
+      <c r="B131" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>34</v>
+      </c>
+      <c r="B132" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>34</v>
+      </c>
+      <c r="B133" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>34</v>
+      </c>
+      <c r="B134" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>34</v>
+      </c>
+      <c r="B135" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>34</v>
+      </c>
+      <c r="B136" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>34</v>
+      </c>
+      <c r="B137" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>34</v>
+      </c>
+      <c r="B138" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11B2B74C-8410-4A88-84B6-55D375344D16}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -7359,7 +8934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{482657F8-43FC-45F9-9834-57F8F380F1AB}">
   <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/src/pages/data/data_corp_demo.xlsx
+++ b/src/pages/data/data_corp_demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/corporate_project/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="178" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBFF0763-671A-4E02-B2FF-3537CD8A5363}"/>
+  <xr:revisionPtr revIDLastSave="229" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F70375B-3FEA-4DF2-9DB2-8F90CB02B876}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="779" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3285" yWindow="3015" windowWidth="15375" windowHeight="7785" tabRatio="917" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_corp" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,8 @@
     <sheet name="data_mercado_basica" sheetId="4" r:id="rId5"/>
     <sheet name="data_mercado_bas_col" sheetId="7" r:id="rId6"/>
     <sheet name="data_mercado_corp" sheetId="5" r:id="rId7"/>
-    <sheet name="data_sae_corp" sheetId="6" r:id="rId8"/>
+    <sheet name="data_col_mat_mercado" sheetId="9" r:id="rId8"/>
+    <sheet name="data_sae_corp" sheetId="6" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_corp!$A$1:$H$229</definedName>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="113">
   <si>
     <t>UNIDAD_ACADEMICA</t>
   </si>
@@ -371,15 +372,36 @@
   <si>
     <t>LICEO MANUEL MARIN</t>
   </si>
+  <si>
+    <t>TIPO</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>MATRICULA</t>
+  </si>
+  <si>
+    <t>ESCUELA ESPAÑA</t>
+  </si>
+  <si>
+    <t>COLEGIO_REF</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -701,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H229"/>
+  <dimension ref="A1:I241"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -714,7 +736,7 @@
     <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -739,8 +761,11 @@
       <c r="H1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -765,8 +790,11 @@
       <c r="H2">
         <v>0.89024390243902396</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -791,8 +819,11 @@
       <c r="H3">
         <v>0.875</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -817,8 +848,11 @@
       <c r="H4">
         <v>0.92307692307692302</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -843,8 +877,11 @@
       <c r="H5">
         <v>0.89285714285714302</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -869,8 +906,11 @@
       <c r="H6">
         <v>0.79591836734693899</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -895,8 +935,11 @@
       <c r="H7">
         <v>0.90566037735849103</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -921,8 +964,11 @@
       <c r="H8">
         <v>0.92592592592592604</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -947,8 +993,11 @@
       <c r="H9">
         <v>0.90090090090090102</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -973,8 +1022,11 @@
       <c r="H10">
         <v>0.92857142857142905</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -999,8 +1051,11 @@
       <c r="H11">
         <v>0.82692307692307698</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1025,8 +1080,11 @@
       <c r="H12">
         <v>0.85333333333333405</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1051,8 +1109,11 @@
       <c r="H13">
         <v>0.77777777777777801</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1077,8 +1138,11 @@
       <c r="H14">
         <v>0.81927710843373502</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1103,8 +1167,11 @@
       <c r="H15">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1129,8 +1196,11 @@
       <c r="H16">
         <v>0.82882882882882902</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -1155,8 +1225,11 @@
       <c r="H17">
         <v>0.78703703703703698</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1181,8 +1254,11 @@
       <c r="H18">
         <v>0.85869565217391297</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1283,11 @@
       <c r="H19">
         <v>0.74468085106382997</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1233,8 +1312,11 @@
       <c r="H20">
         <v>0.84313725490196101</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I20" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -1259,8 +1341,11 @@
       <c r="H21">
         <v>0.82926829268292701</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I21" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -1285,8 +1370,11 @@
       <c r="H22">
         <v>0.87301587301587302</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I22" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1311,8 +1399,11 @@
       <c r="H23">
         <v>0.78</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I23" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -1337,8 +1428,11 @@
       <c r="H24">
         <v>0.843373493975904</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I24" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -1363,8 +1457,11 @@
       <c r="H25">
         <v>0.79487179487179505</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I25" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -1389,8 +1486,11 @@
       <c r="H26">
         <v>0.88695652173912998</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I26" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -1415,8 +1515,11 @@
       <c r="H27">
         <v>0.78640776699029102</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -1441,8 +1544,11 @@
       <c r="H28">
         <v>0.81578947368420995</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I28" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -1467,8 +1573,11 @@
       <c r="H29">
         <v>0.79545454545454597</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I29" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -1493,8 +1602,11 @@
       <c r="H30">
         <v>0.79069767441860495</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1519,8 +1631,11 @@
       <c r="H31">
         <v>0.79104477611940305</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I31" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -1545,8 +1660,11 @@
       <c r="H32">
         <v>0.71212121212121204</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -1571,8 +1689,11 @@
       <c r="H33">
         <v>0.87179487179487203</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I33" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -1597,8 +1718,11 @@
       <c r="H34">
         <v>0.84782608695652195</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I34" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1623,8 +1747,11 @@
       <c r="H35">
         <v>0.76388888888888895</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -1649,8 +1776,11 @@
       <c r="H36">
         <v>0.83</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I36" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -1675,8 +1805,11 @@
       <c r="H37">
         <v>0.73913043478260898</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -1701,8 +1834,11 @@
       <c r="H38">
         <v>0.70833333333333404</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I38" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -1727,8 +1863,11 @@
       <c r="H39">
         <v>0.92500000000000004</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I39" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -1753,8 +1892,11 @@
       <c r="H40">
         <v>0.87037037037037002</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I40" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>7</v>
       </c>
@@ -1779,8 +1921,11 @@
       <c r="H41">
         <v>0.90909090909090895</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I41" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>7</v>
       </c>
@@ -1805,8 +1950,11 @@
       <c r="H42">
         <v>0.8125</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I42" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>7</v>
       </c>
@@ -1831,8 +1979,11 @@
       <c r="H43">
         <v>0.89247311827956999</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I43" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -1857,8 +2008,11 @@
       <c r="H44">
         <v>0.90163934426229497</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I44" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>7</v>
       </c>
@@ -1883,8 +2037,11 @@
       <c r="H45">
         <v>0.91935483870967705</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I45" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1909,8 +2066,11 @@
       <c r="H46">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I46" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -1935,8 +2095,11 @@
       <c r="H47">
         <v>0.875</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I47" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1961,8 +2124,11 @@
       <c r="H48">
         <v>0.86206896551724099</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I48" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -1987,8 +2153,11 @@
       <c r="H49">
         <v>1.0909090909090899</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I49" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -2013,8 +2182,11 @@
       <c r="H50">
         <v>0.88636363636363602</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I50" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -2039,8 +2211,11 @@
       <c r="H51">
         <v>0.82539682539682502</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I51" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -2065,8 +2240,11 @@
       <c r="H52">
         <v>0.87254901960784303</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I52" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -2091,8 +2269,11 @@
       <c r="H53">
         <v>0.93055555555555602</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I53" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -2117,8 +2298,11 @@
       <c r="H54">
         <v>0.85294117647058798</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I54" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>7</v>
       </c>
@@ -2143,8 +2327,11 @@
       <c r="H55">
         <v>0.86666666666666703</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I55" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -2169,8 +2356,11 @@
       <c r="H56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I56" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -2195,8 +2385,11 @@
       <c r="H57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -2221,8 +2414,11 @@
       <c r="H58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I58" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -2247,8 +2443,11 @@
       <c r="H59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I59" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>7</v>
       </c>
@@ -2273,8 +2472,11 @@
       <c r="H60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I60" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -2299,8 +2501,11 @@
       <c r="H61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -2325,8 +2530,11 @@
       <c r="H62">
         <v>0.88571428571428601</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I62" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -2351,8 +2559,11 @@
       <c r="H63">
         <v>0.84210526315789502</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I63" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -2377,8 +2588,11 @@
       <c r="H64">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I64" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -2403,8 +2617,11 @@
       <c r="H65">
         <v>0.86046511627906996</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I65" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -2429,8 +2646,11 @@
       <c r="H66">
         <v>0.82352941176470595</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I66" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -2455,8 +2675,11 @@
       <c r="H67">
         <v>0.83636363636363598</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I67" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -2481,8 +2704,11 @@
       <c r="H68">
         <v>0.86363636363636398</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I68" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -2507,8 +2733,11 @@
       <c r="H69">
         <v>0.70370370370370405</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I69" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -2533,8 +2762,11 @@
       <c r="H70">
         <v>0.811594202898551</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I70" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -2559,8 +2791,11 @@
       <c r="H71">
         <v>0.677966101694915</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I71" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -2585,8 +2820,11 @@
       <c r="H72">
         <v>0.91228070175438603</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I72" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -2611,8 +2849,11 @@
       <c r="H73">
         <v>0.94736842105263197</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I73" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -2637,8 +2878,11 @@
       <c r="H74">
         <v>0.89552238805970197</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I74" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -2663,8 +2907,11 @@
       <c r="H75">
         <v>0.77611940298507498</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I75" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -2689,8 +2936,11 @@
       <c r="H76">
         <v>0.80555555555555602</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I76" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -2715,8 +2965,11 @@
       <c r="H77">
         <v>0.79729729729729704</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I77" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -2741,8 +2994,11 @@
       <c r="H78">
         <v>0.82142857142857095</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I78" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -2767,8 +3023,11 @@
       <c r="H79">
         <v>0.80952380952380998</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I79" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -2793,8 +3052,11 @@
       <c r="H80">
         <v>0.86842105263157898</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I80" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -2819,8 +3081,11 @@
       <c r="H81">
         <v>0.82432432432432401</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I81" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -2845,8 +3110,11 @@
       <c r="H82">
         <v>0.86153846153846203</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I82" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -2871,8 +3139,11 @@
       <c r="H83">
         <v>0.82608695652173902</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I83" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -2897,8 +3168,11 @@
       <c r="H84">
         <v>0.86486486486486502</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I84" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -2923,8 +3197,11 @@
       <c r="H85">
         <v>0.93442622950819698</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I85" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -2949,8 +3226,11 @@
       <c r="H86">
         <v>0.96385542168674698</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I86" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -2975,8 +3255,11 @@
       <c r="H87">
         <v>0.772151898734177</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I87" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -3001,8 +3284,11 @@
       <c r="H88">
         <v>0.80821917808219201</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I88" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -3027,8 +3313,11 @@
       <c r="H89">
         <v>0.84615384615384603</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I89" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -3053,8 +3342,11 @@
       <c r="H90">
         <v>0.89552238805970197</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I90" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -3079,8 +3371,11 @@
       <c r="H91">
         <v>0.88157894736842102</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I91" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -3105,8 +3400,11 @@
       <c r="H92">
         <v>0.88235294117647101</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I92" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -3131,8 +3429,11 @@
       <c r="H93">
         <v>0.82222222222222197</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I93" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -3157,8 +3458,11 @@
       <c r="H94">
         <v>0.68918918918918903</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I94" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -3183,8 +3487,11 @@
       <c r="H95">
         <v>0.84848484848484795</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I95" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -3209,8 +3516,11 @@
       <c r="H96">
         <v>0.84507042253521103</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I96" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -3235,8 +3545,11 @@
       <c r="H97">
         <v>0.86904761904761896</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I97" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -3261,8 +3574,11 @@
       <c r="H98">
         <v>0.89873417721519</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I98" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -3287,8 +3603,11 @@
       <c r="H99">
         <v>0.85882352941176499</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I99" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -3313,8 +3632,11 @@
       <c r="H100">
         <v>0.85555555555555596</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I100" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -3339,8 +3661,11 @@
       <c r="H101">
         <v>0.81690140845070403</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I101" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -3365,8 +3690,11 @@
       <c r="H102">
         <v>0.85135135135135098</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I102" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -3391,8 +3719,11 @@
       <c r="H103">
         <v>0.91428571428571404</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I103" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -3417,8 +3748,11 @@
       <c r="H104">
         <v>0.91011235955056202</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I104" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -3443,8 +3777,11 @@
       <c r="H105">
         <v>0.85555555555555596</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I105" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -3469,8 +3806,11 @@
       <c r="H106">
         <v>0.87640449438202195</v>
       </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I106" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -3495,8 +3835,11 @@
       <c r="H107">
         <v>0.83333333333333404</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I107" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -3521,8 +3864,11 @@
       <c r="H108">
         <v>0.88372093023255804</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I108" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -3547,8 +3893,11 @@
       <c r="H109">
         <v>0.85185185185185197</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I109" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -3573,8 +3922,11 @@
       <c r="H110">
         <v>0.79591836734693899</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I110" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -3599,8 +3951,11 @@
       <c r="H111">
         <v>0.76190476190476197</v>
       </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I111" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -3625,8 +3980,11 @@
       <c r="H112">
         <v>0.88235294117647101</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I112" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -3651,8 +4009,11 @@
       <c r="H113">
         <v>0.88461538461538403</v>
       </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I113" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -3677,8 +4038,11 @@
       <c r="H114">
         <v>0.85416666666666596</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I114" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -3703,8 +4067,11 @@
       <c r="H115">
         <v>0.875</v>
       </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I115" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -3729,8 +4096,11 @@
       <c r="H116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I116" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -3755,8 +4125,11 @@
       <c r="H117">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I117" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -3781,8 +4154,11 @@
       <c r="H118">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I118" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -3807,8 +4183,11 @@
       <c r="H119">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I119" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -3833,8 +4212,11 @@
       <c r="H120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I120" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -3859,8 +4241,11 @@
       <c r="H121">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I121" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>19</v>
       </c>
@@ -3885,8 +4270,11 @@
       <c r="H122">
         <v>0.83050847457627097</v>
       </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I122" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>19</v>
       </c>
@@ -3911,8 +4299,11 @@
       <c r="H123">
         <v>0.86138613861386104</v>
       </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I123" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>19</v>
       </c>
@@ -3937,8 +4328,11 @@
       <c r="H124">
         <v>0.93495934959349603</v>
       </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I124" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>19</v>
       </c>
@@ -3963,8 +4357,11 @@
       <c r="H125">
         <v>0.93700787401574803</v>
       </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I125" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>19</v>
       </c>
@@ -3989,8 +4386,11 @@
       <c r="H126">
         <v>0.93076923076923102</v>
       </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I126" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>19</v>
       </c>
@@ -4015,8 +4415,11 @@
       <c r="H127">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I127" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>19</v>
       </c>
@@ -4041,8 +4444,11 @@
       <c r="H128">
         <v>0.92666666666666597</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I128" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>19</v>
       </c>
@@ -4067,8 +4473,11 @@
       <c r="H129">
         <v>0.97604790419161702</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I129" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>19</v>
       </c>
@@ -4093,8 +4502,11 @@
       <c r="H130">
         <v>0.86734693877550995</v>
       </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I130" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>19</v>
       </c>
@@ -4119,8 +4531,11 @@
       <c r="H131">
         <v>0.80582524271844602</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I131" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>19</v>
       </c>
@@ -4145,8 +4560,11 @@
       <c r="H132">
         <v>0.841584158415842</v>
       </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I132" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>19</v>
       </c>
@@ -4171,8 +4589,11 @@
       <c r="H133">
         <v>0.83464566929133899</v>
       </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I133" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>19</v>
       </c>
@@ -4197,8 +4618,11 @@
       <c r="H134">
         <v>0.85714285714285698</v>
       </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I134" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>19</v>
       </c>
@@ -4223,8 +4647,11 @@
       <c r="H135">
         <v>0.79527559055118102</v>
       </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I135" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>19</v>
       </c>
@@ -4249,8 +4676,11 @@
       <c r="H136">
         <v>0.80597014925373101</v>
       </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I136" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>19</v>
       </c>
@@ -4275,8 +4705,11 @@
       <c r="H137">
         <v>0.85384615384615403</v>
       </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I137" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>19</v>
       </c>
@@ -4301,8 +4734,11 @@
       <c r="H138">
         <v>0.91095890410958902</v>
       </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I138" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>19</v>
       </c>
@@ -4327,8 +4763,11 @@
       <c r="H139">
         <v>0.79710144927536197</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I139" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>19</v>
       </c>
@@ -4353,8 +4792,11 @@
       <c r="H140">
         <v>0.91549295774647899</v>
       </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I140" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>19</v>
       </c>
@@ -4379,8 +4821,11 @@
       <c r="H141">
         <v>0.79807692307692302</v>
       </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I141" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>19</v>
       </c>
@@ -4405,8 +4850,11 @@
       <c r="H142">
         <v>0.822033898305085</v>
       </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I142" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>19</v>
       </c>
@@ -4431,8 +4879,11 @@
       <c r="H143">
         <v>0.845528455284553</v>
       </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I143" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>19</v>
       </c>
@@ -4457,8 +4908,11 @@
       <c r="H144">
         <v>0.88976377952755903</v>
       </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I144" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>19</v>
       </c>
@@ -4483,8 +4937,11 @@
       <c r="H145">
         <v>0.859649122807018</v>
       </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I145" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>19</v>
       </c>
@@ -4509,8 +4966,11 @@
       <c r="H146">
         <v>0.90977443609022601</v>
       </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I146" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>19</v>
       </c>
@@ -4535,8 +4995,11 @@
       <c r="H147">
         <v>0.89677419354838706</v>
       </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I147" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>19</v>
       </c>
@@ -4561,8 +5024,11 @@
       <c r="H148">
         <v>0.83636363636363598</v>
       </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I148" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>19</v>
       </c>
@@ -4587,8 +5053,11 @@
       <c r="H149">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I149" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>19</v>
       </c>
@@ -4613,8 +5082,11 @@
       <c r="H150">
         <v>0.82524271844660202</v>
       </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I150" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>19</v>
       </c>
@@ -4639,8 +5111,11 @@
       <c r="H151">
         <v>0.841584158415842</v>
       </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I151" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>19</v>
       </c>
@@ -4665,8 +5140,11 @@
       <c r="H152">
         <v>0.83333333333333404</v>
       </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I152" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>19</v>
       </c>
@@ -4691,8 +5169,11 @@
       <c r="H153">
         <v>0.855855855855856</v>
       </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I153" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>19</v>
       </c>
@@ -4717,8 +5198,11 @@
       <c r="H154">
         <v>0.86821705426356599</v>
       </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I154" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>19</v>
       </c>
@@ -4743,8 +5227,11 @@
       <c r="H155">
         <v>0.84347826086956501</v>
       </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I155" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>19</v>
       </c>
@@ -4769,8 +5256,11 @@
       <c r="H156">
         <v>0.92156862745098</v>
       </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I156" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>19</v>
       </c>
@@ -4795,8 +5285,11 @@
       <c r="H157">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I157" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>19</v>
       </c>
@@ -4821,8 +5314,11 @@
       <c r="H158">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I158" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>19</v>
       </c>
@@ -4847,8 +5343,11 @@
       <c r="H159">
         <v>0.861788617886179</v>
       </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I159" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>19</v>
       </c>
@@ -4873,8 +5372,11 @@
       <c r="H160">
         <v>0.76470588235294101</v>
       </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I160" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>19</v>
       </c>
@@ -4899,8 +5401,11 @@
       <c r="H161">
         <v>0.81818181818181801</v>
       </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I161" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>19</v>
       </c>
@@ -4925,8 +5430,11 @@
       <c r="H162">
         <v>0.865979381443299</v>
       </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I162" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>19</v>
       </c>
@@ -4951,8 +5459,11 @@
       <c r="H163">
         <v>0.99090909090909096</v>
       </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I163" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>19</v>
       </c>
@@ -4977,8 +5488,11 @@
       <c r="H164">
         <v>0.92035398230088505</v>
       </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I164" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>19</v>
       </c>
@@ -5003,8 +5517,11 @@
       <c r="H165">
         <v>0.92473118279569899</v>
       </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I165" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>19</v>
       </c>
@@ -5029,8 +5546,11 @@
       <c r="H166">
         <v>0.85106382978723405</v>
       </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I166" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>19</v>
       </c>
@@ -5055,8 +5575,11 @@
       <c r="H167">
         <v>0.98148148148148195</v>
       </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I167" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>19</v>
       </c>
@@ -5081,8 +5604,11 @@
       <c r="H168">
         <v>0.94399999999999995</v>
       </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I168" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>19</v>
       </c>
@@ -5107,8 +5633,11 @@
       <c r="H169">
         <v>0.92134831460674205</v>
       </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I169" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>19</v>
       </c>
@@ -5133,8 +5662,11 @@
       <c r="H170">
         <v>0.85714285714285698</v>
       </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I170" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>19</v>
       </c>
@@ -5159,8 +5691,11 @@
       <c r="H171">
         <v>0.90839694656488601</v>
       </c>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I171" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>19</v>
       </c>
@@ -5185,8 +5720,11 @@
       <c r="H172">
         <v>0.838095238095238</v>
       </c>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I172" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>19</v>
       </c>
@@ -5211,8 +5749,11 @@
       <c r="H173">
         <v>0.855855855855856</v>
       </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I173" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>19</v>
       </c>
@@ -5237,8 +5778,11 @@
       <c r="H174">
         <v>0.88549618320610701</v>
       </c>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I174" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>19</v>
       </c>
@@ -5263,8 +5807,11 @@
       <c r="H175">
         <v>0.91176470588235303</v>
       </c>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I175" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>19</v>
       </c>
@@ -5289,8 +5836,11 @@
       <c r="H176">
         <v>0</v>
       </c>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I176" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>19</v>
       </c>
@@ -5315,8 +5865,11 @@
       <c r="H177">
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I177" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>19</v>
       </c>
@@ -5341,8 +5894,11 @@
       <c r="H178">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I178" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>19</v>
       </c>
@@ -5367,8 +5923,11 @@
       <c r="H179">
         <v>0</v>
       </c>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I179" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>19</v>
       </c>
@@ -5393,8 +5952,11 @@
       <c r="H180">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I180" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>19</v>
       </c>
@@ -5419,8 +5981,11 @@
       <c r="H181">
         <v>0</v>
       </c>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I181" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>20</v>
       </c>
@@ -5445,8 +6010,11 @@
       <c r="H182">
         <v>0.71707317073170729</v>
       </c>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I182" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>20</v>
       </c>
@@ -5471,8 +6039,11 @@
       <c r="H183">
         <v>0.94357366771159878</v>
       </c>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I183" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>20</v>
       </c>
@@ -5497,8 +6068,11 @@
       <c r="H184">
         <v>0.89508196721311473</v>
       </c>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I184" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>20</v>
       </c>
@@ -5523,8 +6097,11 @@
       <c r="H185">
         <v>0.96498054474708173</v>
       </c>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I185" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>20</v>
       </c>
@@ -5549,8 +6126,11 @@
       <c r="H186">
         <v>0.60396039603960394</v>
       </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I186" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>20</v>
       </c>
@@ -5575,8 +6155,11 @@
       <c r="H187">
         <v>0.81481481481481477</v>
       </c>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I187" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>20</v>
       </c>
@@ -5601,8 +6184,11 @@
       <c r="H188">
         <v>0.84776119402985073</v>
       </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I188" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>20</v>
       </c>
@@ -5627,8 +6213,11 @@
       <c r="H189">
         <v>0.93602693602693599</v>
       </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I189" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>20</v>
       </c>
@@ -5653,8 +6242,11 @@
       <c r="H190">
         <v>0.57948717948717954</v>
       </c>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I190" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>20</v>
       </c>
@@ -5679,8 +6271,11 @@
       <c r="H191">
         <v>0.71480144404332135</v>
       </c>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I191" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>20</v>
       </c>
@@ -5705,8 +6300,11 @@
       <c r="H192">
         <v>0.81543624161073824</v>
       </c>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I192" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>20</v>
       </c>
@@ -5731,34 +6329,40 @@
       <c r="H193">
         <v>0.9088050314465409</v>
       </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
+      <c r="I193" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B194">
+      <c r="B194" s="2">
         <v>2024</v>
       </c>
-      <c r="C194" t="s">
+      <c r="C194" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D194">
+      <c r="D194" s="2">
         <v>132</v>
       </c>
-      <c r="E194">
+      <c r="E194" s="2">
         <v>5</v>
       </c>
-      <c r="F194">
+      <c r="F194" s="2">
         <v>176</v>
       </c>
-      <c r="G194">
+      <c r="G194" s="2">
         <v>208</v>
       </c>
-      <c r="H194">
+      <c r="H194" s="2">
         <v>0.65865384615384615</v>
       </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I194" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>20</v>
       </c>
@@ -5783,8 +6387,11 @@
       <c r="H195">
         <v>0.77533039647577096</v>
       </c>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I195" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>20</v>
       </c>
@@ -5809,8 +6416,11 @@
       <c r="H196">
         <v>0.86343612334801767</v>
       </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I196" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>20</v>
       </c>
@@ -5835,8 +6445,11 @@
       <c r="H197">
         <v>0.94117647058823528</v>
       </c>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I197" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>20</v>
       </c>
@@ -5861,8 +6474,11 @@
       <c r="H198">
         <v>0.74603174603174605</v>
       </c>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I198" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>20</v>
       </c>
@@ -5887,8 +6503,11 @@
       <c r="H199">
         <v>0.81150159744408945</v>
       </c>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I199" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>20</v>
       </c>
@@ -5913,8 +6532,11 @@
       <c r="H200">
         <v>0.80973451327433632</v>
       </c>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I200" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>20</v>
       </c>
@@ -5939,8 +6561,11 @@
       <c r="H201">
         <v>0.91633466135458164</v>
       </c>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I201" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>20</v>
       </c>
@@ -5965,8 +6590,11 @@
       <c r="H202">
         <v>0.81481481481481477</v>
       </c>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I202" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>20</v>
       </c>
@@ -5991,8 +6619,11 @@
       <c r="H203">
         <v>0.87147335423197492</v>
       </c>
-    </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I203" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>20</v>
       </c>
@@ -6017,8 +6648,11 @@
       <c r="H204">
         <v>0.94545454545454544</v>
       </c>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I204" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>20</v>
       </c>
@@ -6043,8 +6677,11 @@
       <c r="H205">
         <v>0.70652173913043481</v>
       </c>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I205" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>25</v>
       </c>
@@ -6069,8 +6706,11 @@
       <c r="H206">
         <v>0.81927710843373502</v>
       </c>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I206" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>25</v>
       </c>
@@ -6095,8 +6735,11 @@
       <c r="H207">
         <v>0.92307692307692302</v>
       </c>
-    </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I207" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>25</v>
       </c>
@@ -6121,8 +6764,11 @@
       <c r="H208">
         <v>0.90987124463519298</v>
       </c>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I208" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>25</v>
       </c>
@@ -6147,8 +6793,11 @@
       <c r="H209">
         <v>0.91780821917808197</v>
       </c>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I209" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>25</v>
       </c>
@@ -6173,8 +6822,11 @@
       <c r="H210">
         <v>0.72131147540983598</v>
       </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I210" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>25</v>
       </c>
@@ -6199,8 +6851,11 @@
       <c r="H211">
         <v>0.80930232558139503</v>
       </c>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I211" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>25</v>
       </c>
@@ -6225,8 +6880,11 @@
       <c r="H212">
         <v>0.78341013824884798</v>
       </c>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I212" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>25</v>
       </c>
@@ -6251,8 +6909,11 @@
       <c r="H213">
         <v>0.91228070175438603</v>
       </c>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I213" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>25</v>
       </c>
@@ -6277,8 +6938,11 @@
       <c r="H214">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I214" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>25</v>
       </c>
@@ -6303,8 +6967,11 @@
       <c r="H215">
         <v>0.79916317991631802</v>
       </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I215" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>25</v>
       </c>
@@ -6329,8 +6996,11 @@
       <c r="H216">
         <v>0.82587064676616895</v>
       </c>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I216" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>25</v>
       </c>
@@ -6355,8 +7025,11 @@
       <c r="H217">
         <v>0.949238578680203</v>
       </c>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I217" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>25</v>
       </c>
@@ -6381,8 +7054,11 @@
       <c r="H218">
         <v>0.648484848484848</v>
       </c>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I218" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>25</v>
       </c>
@@ -6407,8 +7083,11 @@
       <c r="H219">
         <v>0.79444444444444395</v>
       </c>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I219" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>25</v>
       </c>
@@ -6433,8 +7112,11 @@
       <c r="H220">
         <v>0.80341880341880401</v>
       </c>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I220" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>25</v>
       </c>
@@ -6459,8 +7141,11 @@
       <c r="H221">
         <v>0.93034825870646798</v>
       </c>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I221" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>25</v>
       </c>
@@ -6485,8 +7170,11 @@
       <c r="H222">
         <v>0.73291925465838503</v>
       </c>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I222" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>25</v>
       </c>
@@ -6511,8 +7199,11 @@
       <c r="H223">
         <v>0.82352941176470595</v>
       </c>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I223" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>25</v>
       </c>
@@ -6537,8 +7228,11 @@
       <c r="H224">
         <v>0.86592178770949702</v>
       </c>
-    </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I224" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>25</v>
       </c>
@@ -6563,8 +7257,11 @@
       <c r="H225">
         <v>0.93273542600896897</v>
       </c>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I225" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>25</v>
       </c>
@@ -6589,8 +7286,11 @@
       <c r="H226">
         <v>0.84134615384615397</v>
       </c>
-    </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I226" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>25</v>
       </c>
@@ -6615,8 +7315,11 @@
       <c r="H227">
         <v>0.89252336448598102</v>
       </c>
-    </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I227" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>25</v>
       </c>
@@ -6641,8 +7344,11 @@
       <c r="H228">
         <v>0.91284403669724801</v>
       </c>
-    </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I228" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>25</v>
       </c>
@@ -6667,8 +7373,216 @@
       <c r="H229">
         <v>0.76760563380281699</v>
       </c>
+      <c r="I229" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>20</v>
+      </c>
+      <c r="B230">
+        <v>2021</v>
+      </c>
+      <c r="C230" t="s">
+        <v>24</v>
+      </c>
+      <c r="H230">
+        <v>0.63865546218487401</v>
+      </c>
+      <c r="I230" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>20</v>
+      </c>
+      <c r="B231">
+        <v>2022</v>
+      </c>
+      <c r="C231" t="s">
+        <v>24</v>
+      </c>
+      <c r="H231">
+        <v>0.46428571428571402</v>
+      </c>
+      <c r="I231" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>20</v>
+      </c>
+      <c r="B232">
+        <v>2023</v>
+      </c>
+      <c r="C232" t="s">
+        <v>24</v>
+      </c>
+      <c r="H232">
+        <v>0.46226415094339601</v>
+      </c>
+      <c r="I232" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>20</v>
+      </c>
+      <c r="B233">
+        <v>2024</v>
+      </c>
+      <c r="C233" t="s">
+        <v>24</v>
+      </c>
+      <c r="H233">
+        <v>0.56779661016949201</v>
+      </c>
+      <c r="I233" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>20</v>
+      </c>
+      <c r="B234">
+        <v>2025</v>
+      </c>
+      <c r="C234" t="s">
+        <v>24</v>
+      </c>
+      <c r="H234">
+        <v>0.65</v>
+      </c>
+      <c r="I234" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>20</v>
+      </c>
+      <c r="B235">
+        <v>2026</v>
+      </c>
+      <c r="C235" t="s">
+        <v>24</v>
+      </c>
+      <c r="H235">
+        <v>0.55319148936170204</v>
+      </c>
+      <c r="I235" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>20</v>
+      </c>
+      <c r="B236">
+        <v>2021</v>
+      </c>
+      <c r="C236" t="s">
+        <v>24</v>
+      </c>
+      <c r="H236">
+        <v>0.82558139534883701</v>
+      </c>
+      <c r="I236" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>20</v>
+      </c>
+      <c r="B237">
+        <v>2022</v>
+      </c>
+      <c r="C237" t="s">
+        <v>24</v>
+      </c>
+      <c r="H237">
+        <v>0.74444444444444402</v>
+      </c>
+      <c r="I237" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>20</v>
+      </c>
+      <c r="B238">
+        <v>2023</v>
+      </c>
+      <c r="C238" t="s">
+        <v>24</v>
+      </c>
+      <c r="H238">
+        <v>0.71910112359550604</v>
+      </c>
+      <c r="I238" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>20</v>
+      </c>
+      <c r="B239">
+        <v>2024</v>
+      </c>
+      <c r="C239" t="s">
+        <v>24</v>
+      </c>
+      <c r="H239">
+        <v>0.77777777777777801</v>
+      </c>
+      <c r="I239" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>20</v>
+      </c>
+      <c r="B240">
+        <v>2025</v>
+      </c>
+      <c r="C240" t="s">
+        <v>24</v>
+      </c>
+      <c r="H240">
+        <v>0.82022471910112404</v>
+      </c>
+      <c r="I240" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>20</v>
+      </c>
+      <c r="B241">
+        <v>2026</v>
+      </c>
+      <c r="C241" t="s">
+        <v>24</v>
+      </c>
+      <c r="H241">
+        <v>0.82222222222222197</v>
+      </c>
+      <c r="I241" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6689,9 +7603,9 @@
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -8935,6 +9849,2724 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{698C1C06-077D-4280-80CF-7D6AE0F9E340}">
+  <dimension ref="A1:D193"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2">
+        <v>2020</v>
+      </c>
+      <c r="C2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>2021</v>
+      </c>
+      <c r="C3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4">
+        <v>2022</v>
+      </c>
+      <c r="C4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>2023</v>
+      </c>
+      <c r="C5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>2024</v>
+      </c>
+      <c r="C6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7">
+        <v>2025</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8">
+        <v>2020</v>
+      </c>
+      <c r="C8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>2021</v>
+      </c>
+      <c r="C9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10">
+        <v>2022</v>
+      </c>
+      <c r="C10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <v>2023</v>
+      </c>
+      <c r="C11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12">
+        <v>2024</v>
+      </c>
+      <c r="C12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13">
+        <v>2025</v>
+      </c>
+      <c r="C13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14">
+        <v>2020</v>
+      </c>
+      <c r="C14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15">
+        <v>2021</v>
+      </c>
+      <c r="C15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16">
+        <v>2022</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17">
+        <v>2023</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18">
+        <v>2024</v>
+      </c>
+      <c r="C18" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <v>2025</v>
+      </c>
+      <c r="C19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>2020</v>
+      </c>
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>2021</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>2022</v>
+      </c>
+      <c r="C22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23">
+        <v>2023</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24">
+        <v>2024</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25">
+        <v>2025</v>
+      </c>
+      <c r="C25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26">
+        <v>2020</v>
+      </c>
+      <c r="C26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27">
+        <v>2021</v>
+      </c>
+      <c r="C27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28">
+        <v>2022</v>
+      </c>
+      <c r="C28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29">
+        <v>2023</v>
+      </c>
+      <c r="C29" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30">
+        <v>2024</v>
+      </c>
+      <c r="C30" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31">
+        <v>2025</v>
+      </c>
+      <c r="C31" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32">
+        <v>2020</v>
+      </c>
+      <c r="C32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33">
+        <v>2021</v>
+      </c>
+      <c r="C33" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34">
+        <v>2022</v>
+      </c>
+      <c r="C34" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35">
+        <v>2023</v>
+      </c>
+      <c r="C35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36">
+        <v>2024</v>
+      </c>
+      <c r="C36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37">
+        <v>2025</v>
+      </c>
+      <c r="C37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38">
+        <v>2020</v>
+      </c>
+      <c r="C38" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39">
+        <v>2021</v>
+      </c>
+      <c r="C39" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40">
+        <v>2022</v>
+      </c>
+      <c r="C40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41">
+        <v>2023</v>
+      </c>
+      <c r="C41" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42">
+        <v>2024</v>
+      </c>
+      <c r="C42" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43">
+        <v>2025</v>
+      </c>
+      <c r="C43" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44">
+        <v>2020</v>
+      </c>
+      <c r="C44" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45">
+        <v>2021</v>
+      </c>
+      <c r="C45" t="s">
+        <v>59</v>
+      </c>
+      <c r="D45">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46">
+        <v>2022</v>
+      </c>
+      <c r="C46" t="s">
+        <v>59</v>
+      </c>
+      <c r="D46">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47">
+        <v>2023</v>
+      </c>
+      <c r="C47" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48">
+        <v>2024</v>
+      </c>
+      <c r="C48" t="s">
+        <v>59</v>
+      </c>
+      <c r="D48">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49">
+        <v>2025</v>
+      </c>
+      <c r="C49" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50">
+        <v>2020</v>
+      </c>
+      <c r="C50" t="s">
+        <v>111</v>
+      </c>
+      <c r="D50">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51">
+        <v>2021</v>
+      </c>
+      <c r="C51" t="s">
+        <v>111</v>
+      </c>
+      <c r="D51">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52">
+        <v>2022</v>
+      </c>
+      <c r="C52" t="s">
+        <v>111</v>
+      </c>
+      <c r="D52">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53">
+        <v>2023</v>
+      </c>
+      <c r="C53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D53">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54">
+        <v>2024</v>
+      </c>
+      <c r="C54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>18</v>
+      </c>
+      <c r="B55">
+        <v>2025</v>
+      </c>
+      <c r="C55" t="s">
+        <v>111</v>
+      </c>
+      <c r="D55">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>18</v>
+      </c>
+      <c r="B56">
+        <v>2020</v>
+      </c>
+      <c r="C56" t="s">
+        <v>52</v>
+      </c>
+      <c r="D56">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57">
+        <v>2021</v>
+      </c>
+      <c r="C57" t="s">
+        <v>52</v>
+      </c>
+      <c r="D57">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58">
+        <v>2022</v>
+      </c>
+      <c r="C58" t="s">
+        <v>52</v>
+      </c>
+      <c r="D58">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59">
+        <v>2023</v>
+      </c>
+      <c r="C59" t="s">
+        <v>52</v>
+      </c>
+      <c r="D59">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>18</v>
+      </c>
+      <c r="B60">
+        <v>2024</v>
+      </c>
+      <c r="C60" t="s">
+        <v>52</v>
+      </c>
+      <c r="D60">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61">
+        <v>2025</v>
+      </c>
+      <c r="C61" t="s">
+        <v>52</v>
+      </c>
+      <c r="D61">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>18</v>
+      </c>
+      <c r="B62">
+        <v>2020</v>
+      </c>
+      <c r="C62" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>18</v>
+      </c>
+      <c r="B63">
+        <v>2021</v>
+      </c>
+      <c r="C63" t="s">
+        <v>56</v>
+      </c>
+      <c r="D63">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64">
+        <v>2022</v>
+      </c>
+      <c r="C64" t="s">
+        <v>56</v>
+      </c>
+      <c r="D64">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>18</v>
+      </c>
+      <c r="B65">
+        <v>2023</v>
+      </c>
+      <c r="C65" t="s">
+        <v>56</v>
+      </c>
+      <c r="D65">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>18</v>
+      </c>
+      <c r="B66">
+        <v>2024</v>
+      </c>
+      <c r="C66" t="s">
+        <v>56</v>
+      </c>
+      <c r="D66">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>18</v>
+      </c>
+      <c r="B67">
+        <v>2025</v>
+      </c>
+      <c r="C67" t="s">
+        <v>56</v>
+      </c>
+      <c r="D67">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>18</v>
+      </c>
+      <c r="B68">
+        <v>2020</v>
+      </c>
+      <c r="C68" t="s">
+        <v>59</v>
+      </c>
+      <c r="D68">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>18</v>
+      </c>
+      <c r="B69">
+        <v>2021</v>
+      </c>
+      <c r="C69" t="s">
+        <v>59</v>
+      </c>
+      <c r="D69">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>18</v>
+      </c>
+      <c r="B70">
+        <v>2022</v>
+      </c>
+      <c r="C70" t="s">
+        <v>59</v>
+      </c>
+      <c r="D70">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>18</v>
+      </c>
+      <c r="B71">
+        <v>2023</v>
+      </c>
+      <c r="C71" t="s">
+        <v>59</v>
+      </c>
+      <c r="D71">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>18</v>
+      </c>
+      <c r="B72">
+        <v>2024</v>
+      </c>
+      <c r="C72" t="s">
+        <v>59</v>
+      </c>
+      <c r="D72">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>18</v>
+      </c>
+      <c r="B73">
+        <v>2025</v>
+      </c>
+      <c r="C73" t="s">
+        <v>59</v>
+      </c>
+      <c r="D73">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>31</v>
+      </c>
+      <c r="B74">
+        <v>2020</v>
+      </c>
+      <c r="C74" t="s">
+        <v>75</v>
+      </c>
+      <c r="D74">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>31</v>
+      </c>
+      <c r="B75">
+        <v>2021</v>
+      </c>
+      <c r="C75" t="s">
+        <v>75</v>
+      </c>
+      <c r="D75">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>31</v>
+      </c>
+      <c r="B76">
+        <v>2022</v>
+      </c>
+      <c r="C76" t="s">
+        <v>75</v>
+      </c>
+      <c r="D76">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>31</v>
+      </c>
+      <c r="B77">
+        <v>2023</v>
+      </c>
+      <c r="C77" t="s">
+        <v>75</v>
+      </c>
+      <c r="D77">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>31</v>
+      </c>
+      <c r="B78">
+        <v>2024</v>
+      </c>
+      <c r="C78" t="s">
+        <v>75</v>
+      </c>
+      <c r="D78">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>31</v>
+      </c>
+      <c r="B79">
+        <v>2025</v>
+      </c>
+      <c r="C79" t="s">
+        <v>75</v>
+      </c>
+      <c r="D79">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>31</v>
+      </c>
+      <c r="B80">
+        <v>2020</v>
+      </c>
+      <c r="C80" t="s">
+        <v>72</v>
+      </c>
+      <c r="D80">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>31</v>
+      </c>
+      <c r="B81">
+        <v>2021</v>
+      </c>
+      <c r="C81" t="s">
+        <v>72</v>
+      </c>
+      <c r="D81">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>31</v>
+      </c>
+      <c r="B82">
+        <v>2022</v>
+      </c>
+      <c r="C82" t="s">
+        <v>72</v>
+      </c>
+      <c r="D82">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>31</v>
+      </c>
+      <c r="B83">
+        <v>2023</v>
+      </c>
+      <c r="C83" t="s">
+        <v>72</v>
+      </c>
+      <c r="D83">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>31</v>
+      </c>
+      <c r="B84">
+        <v>2024</v>
+      </c>
+      <c r="C84" t="s">
+        <v>72</v>
+      </c>
+      <c r="D84">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>31</v>
+      </c>
+      <c r="B85">
+        <v>2025</v>
+      </c>
+      <c r="C85" t="s">
+        <v>72</v>
+      </c>
+      <c r="D85">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>31</v>
+      </c>
+      <c r="B86">
+        <v>2020</v>
+      </c>
+      <c r="C86" t="s">
+        <v>69</v>
+      </c>
+      <c r="D86">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>31</v>
+      </c>
+      <c r="B87">
+        <v>2021</v>
+      </c>
+      <c r="C87" t="s">
+        <v>69</v>
+      </c>
+      <c r="D87">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B88">
+        <v>2022</v>
+      </c>
+      <c r="C88" t="s">
+        <v>69</v>
+      </c>
+      <c r="D88">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>31</v>
+      </c>
+      <c r="B89">
+        <v>2023</v>
+      </c>
+      <c r="C89" t="s">
+        <v>69</v>
+      </c>
+      <c r="D89">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>31</v>
+      </c>
+      <c r="B90">
+        <v>2024</v>
+      </c>
+      <c r="C90" t="s">
+        <v>69</v>
+      </c>
+      <c r="D90">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>31</v>
+      </c>
+      <c r="B91">
+        <v>2025</v>
+      </c>
+      <c r="C91" t="s">
+        <v>69</v>
+      </c>
+      <c r="D91">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>31</v>
+      </c>
+      <c r="B92">
+        <v>2020</v>
+      </c>
+      <c r="C92" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>31</v>
+      </c>
+      <c r="B93">
+        <v>2021</v>
+      </c>
+      <c r="C93" t="s">
+        <v>68</v>
+      </c>
+      <c r="D93">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>31</v>
+      </c>
+      <c r="B94">
+        <v>2022</v>
+      </c>
+      <c r="C94" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>31</v>
+      </c>
+      <c r="B95">
+        <v>2023</v>
+      </c>
+      <c r="C95" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>31</v>
+      </c>
+      <c r="B96">
+        <v>2024</v>
+      </c>
+      <c r="C96" t="s">
+        <v>68</v>
+      </c>
+      <c r="D96">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>31</v>
+      </c>
+      <c r="B97">
+        <v>2025</v>
+      </c>
+      <c r="C97" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>32</v>
+      </c>
+      <c r="B98">
+        <v>2020</v>
+      </c>
+      <c r="C98" t="s">
+        <v>111</v>
+      </c>
+      <c r="D98">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>32</v>
+      </c>
+      <c r="B99">
+        <v>2021</v>
+      </c>
+      <c r="C99" t="s">
+        <v>111</v>
+      </c>
+      <c r="D99">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>32</v>
+      </c>
+      <c r="B100">
+        <v>2022</v>
+      </c>
+      <c r="C100" t="s">
+        <v>111</v>
+      </c>
+      <c r="D100">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>32</v>
+      </c>
+      <c r="B101">
+        <v>2023</v>
+      </c>
+      <c r="C101" t="s">
+        <v>111</v>
+      </c>
+      <c r="D101">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>32</v>
+      </c>
+      <c r="B102">
+        <v>2024</v>
+      </c>
+      <c r="C102" t="s">
+        <v>111</v>
+      </c>
+      <c r="D102">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>32</v>
+      </c>
+      <c r="B103">
+        <v>2025</v>
+      </c>
+      <c r="C103" t="s">
+        <v>111</v>
+      </c>
+      <c r="D103">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>32</v>
+      </c>
+      <c r="B104">
+        <v>2020</v>
+      </c>
+      <c r="C104" t="s">
+        <v>52</v>
+      </c>
+      <c r="D104">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>32</v>
+      </c>
+      <c r="B105">
+        <v>2021</v>
+      </c>
+      <c r="C105" t="s">
+        <v>52</v>
+      </c>
+      <c r="D105">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>32</v>
+      </c>
+      <c r="B106">
+        <v>2022</v>
+      </c>
+      <c r="C106" t="s">
+        <v>52</v>
+      </c>
+      <c r="D106">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>32</v>
+      </c>
+      <c r="B107">
+        <v>2023</v>
+      </c>
+      <c r="C107" t="s">
+        <v>52</v>
+      </c>
+      <c r="D107">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>32</v>
+      </c>
+      <c r="B108">
+        <v>2024</v>
+      </c>
+      <c r="C108" t="s">
+        <v>52</v>
+      </c>
+      <c r="D108">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>32</v>
+      </c>
+      <c r="B109">
+        <v>2025</v>
+      </c>
+      <c r="C109" t="s">
+        <v>52</v>
+      </c>
+      <c r="D109">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>32</v>
+      </c>
+      <c r="B110">
+        <v>2020</v>
+      </c>
+      <c r="C110" t="s">
+        <v>56</v>
+      </c>
+      <c r="D110">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>32</v>
+      </c>
+      <c r="B111">
+        <v>2021</v>
+      </c>
+      <c r="C111" t="s">
+        <v>56</v>
+      </c>
+      <c r="D111">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>32</v>
+      </c>
+      <c r="B112">
+        <v>2022</v>
+      </c>
+      <c r="C112" t="s">
+        <v>56</v>
+      </c>
+      <c r="D112">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>32</v>
+      </c>
+      <c r="B113">
+        <v>2023</v>
+      </c>
+      <c r="C113" t="s">
+        <v>56</v>
+      </c>
+      <c r="D113">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>32</v>
+      </c>
+      <c r="B114">
+        <v>2024</v>
+      </c>
+      <c r="C114" t="s">
+        <v>56</v>
+      </c>
+      <c r="D114">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>32</v>
+      </c>
+      <c r="B115">
+        <v>2025</v>
+      </c>
+      <c r="C115" t="s">
+        <v>56</v>
+      </c>
+      <c r="D115">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>32</v>
+      </c>
+      <c r="B116">
+        <v>2020</v>
+      </c>
+      <c r="C116" t="s">
+        <v>59</v>
+      </c>
+      <c r="D116">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>32</v>
+      </c>
+      <c r="B117">
+        <v>2021</v>
+      </c>
+      <c r="C117" t="s">
+        <v>59</v>
+      </c>
+      <c r="D117">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>32</v>
+      </c>
+      <c r="B118">
+        <v>2022</v>
+      </c>
+      <c r="C118" t="s">
+        <v>59</v>
+      </c>
+      <c r="D118">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>32</v>
+      </c>
+      <c r="B119">
+        <v>2023</v>
+      </c>
+      <c r="C119" t="s">
+        <v>59</v>
+      </c>
+      <c r="D119">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>32</v>
+      </c>
+      <c r="B120">
+        <v>2024</v>
+      </c>
+      <c r="C120" t="s">
+        <v>59</v>
+      </c>
+      <c r="D120">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>32</v>
+      </c>
+      <c r="B121">
+        <v>2025</v>
+      </c>
+      <c r="C121" t="s">
+        <v>59</v>
+      </c>
+      <c r="D121">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>33</v>
+      </c>
+      <c r="B122">
+        <v>2020</v>
+      </c>
+      <c r="C122" t="s">
+        <v>111</v>
+      </c>
+      <c r="D122">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>33</v>
+      </c>
+      <c r="B123">
+        <v>2021</v>
+      </c>
+      <c r="C123" t="s">
+        <v>111</v>
+      </c>
+      <c r="D123">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>33</v>
+      </c>
+      <c r="B124">
+        <v>2022</v>
+      </c>
+      <c r="C124" t="s">
+        <v>111</v>
+      </c>
+      <c r="D124">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>33</v>
+      </c>
+      <c r="B125">
+        <v>2023</v>
+      </c>
+      <c r="C125" t="s">
+        <v>111</v>
+      </c>
+      <c r="D125">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>33</v>
+      </c>
+      <c r="B126">
+        <v>2024</v>
+      </c>
+      <c r="C126" t="s">
+        <v>111</v>
+      </c>
+      <c r="D126">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>33</v>
+      </c>
+      <c r="B127">
+        <v>2025</v>
+      </c>
+      <c r="C127" t="s">
+        <v>111</v>
+      </c>
+      <c r="D127">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>33</v>
+      </c>
+      <c r="B128">
+        <v>2020</v>
+      </c>
+      <c r="C128" t="s">
+        <v>52</v>
+      </c>
+      <c r="D128">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>33</v>
+      </c>
+      <c r="B129">
+        <v>2021</v>
+      </c>
+      <c r="C129" t="s">
+        <v>52</v>
+      </c>
+      <c r="D129">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>33</v>
+      </c>
+      <c r="B130">
+        <v>2022</v>
+      </c>
+      <c r="C130" t="s">
+        <v>52</v>
+      </c>
+      <c r="D130">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>33</v>
+      </c>
+      <c r="B131">
+        <v>2023</v>
+      </c>
+      <c r="C131" t="s">
+        <v>52</v>
+      </c>
+      <c r="D131">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>33</v>
+      </c>
+      <c r="B132">
+        <v>2024</v>
+      </c>
+      <c r="C132" t="s">
+        <v>52</v>
+      </c>
+      <c r="D132">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>33</v>
+      </c>
+      <c r="B133">
+        <v>2025</v>
+      </c>
+      <c r="C133" t="s">
+        <v>52</v>
+      </c>
+      <c r="D133">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>33</v>
+      </c>
+      <c r="B134">
+        <v>2020</v>
+      </c>
+      <c r="C134" t="s">
+        <v>56</v>
+      </c>
+      <c r="D134">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>33</v>
+      </c>
+      <c r="B135">
+        <v>2021</v>
+      </c>
+      <c r="C135" t="s">
+        <v>56</v>
+      </c>
+      <c r="D135">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>33</v>
+      </c>
+      <c r="B136">
+        <v>2022</v>
+      </c>
+      <c r="C136" t="s">
+        <v>56</v>
+      </c>
+      <c r="D136">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>33</v>
+      </c>
+      <c r="B137">
+        <v>2023</v>
+      </c>
+      <c r="C137" t="s">
+        <v>56</v>
+      </c>
+      <c r="D137">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>33</v>
+      </c>
+      <c r="B138">
+        <v>2024</v>
+      </c>
+      <c r="C138" t="s">
+        <v>56</v>
+      </c>
+      <c r="D138">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>33</v>
+      </c>
+      <c r="B139">
+        <v>2025</v>
+      </c>
+      <c r="C139" t="s">
+        <v>56</v>
+      </c>
+      <c r="D139">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>33</v>
+      </c>
+      <c r="B140">
+        <v>2020</v>
+      </c>
+      <c r="C140" t="s">
+        <v>59</v>
+      </c>
+      <c r="D140">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>33</v>
+      </c>
+      <c r="B141">
+        <v>2021</v>
+      </c>
+      <c r="C141" t="s">
+        <v>59</v>
+      </c>
+      <c r="D141">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>33</v>
+      </c>
+      <c r="B142">
+        <v>2022</v>
+      </c>
+      <c r="C142" t="s">
+        <v>59</v>
+      </c>
+      <c r="D142">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>33</v>
+      </c>
+      <c r="B143">
+        <v>2023</v>
+      </c>
+      <c r="C143" t="s">
+        <v>59</v>
+      </c>
+      <c r="D143">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>33</v>
+      </c>
+      <c r="B144">
+        <v>2024</v>
+      </c>
+      <c r="C144" t="s">
+        <v>59</v>
+      </c>
+      <c r="D144">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>33</v>
+      </c>
+      <c r="B145">
+        <v>2025</v>
+      </c>
+      <c r="C145" t="s">
+        <v>59</v>
+      </c>
+      <c r="D145">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>34</v>
+      </c>
+      <c r="B146">
+        <v>2020</v>
+      </c>
+      <c r="C146" t="s">
+        <v>75</v>
+      </c>
+      <c r="D146">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>34</v>
+      </c>
+      <c r="B147">
+        <v>2021</v>
+      </c>
+      <c r="C147" t="s">
+        <v>75</v>
+      </c>
+      <c r="D147">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>34</v>
+      </c>
+      <c r="B148">
+        <v>2022</v>
+      </c>
+      <c r="C148" t="s">
+        <v>75</v>
+      </c>
+      <c r="D148">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>34</v>
+      </c>
+      <c r="B149">
+        <v>2023</v>
+      </c>
+      <c r="C149" t="s">
+        <v>75</v>
+      </c>
+      <c r="D149">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>34</v>
+      </c>
+      <c r="B150">
+        <v>2024</v>
+      </c>
+      <c r="C150" t="s">
+        <v>75</v>
+      </c>
+      <c r="D150">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>34</v>
+      </c>
+      <c r="B151">
+        <v>2025</v>
+      </c>
+      <c r="C151" t="s">
+        <v>75</v>
+      </c>
+      <c r="D151">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>34</v>
+      </c>
+      <c r="B152">
+        <v>2020</v>
+      </c>
+      <c r="C152" t="s">
+        <v>72</v>
+      </c>
+      <c r="D152">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>34</v>
+      </c>
+      <c r="B153">
+        <v>2021</v>
+      </c>
+      <c r="C153" t="s">
+        <v>72</v>
+      </c>
+      <c r="D153">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>34</v>
+      </c>
+      <c r="B154">
+        <v>2022</v>
+      </c>
+      <c r="C154" t="s">
+        <v>72</v>
+      </c>
+      <c r="D154">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>34</v>
+      </c>
+      <c r="B155">
+        <v>2023</v>
+      </c>
+      <c r="C155" t="s">
+        <v>72</v>
+      </c>
+      <c r="D155">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>34</v>
+      </c>
+      <c r="B156">
+        <v>2024</v>
+      </c>
+      <c r="C156" t="s">
+        <v>72</v>
+      </c>
+      <c r="D156">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>34</v>
+      </c>
+      <c r="B157">
+        <v>2025</v>
+      </c>
+      <c r="C157" t="s">
+        <v>72</v>
+      </c>
+      <c r="D157">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>34</v>
+      </c>
+      <c r="B158">
+        <v>2020</v>
+      </c>
+      <c r="C158" t="s">
+        <v>69</v>
+      </c>
+      <c r="D158">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>34</v>
+      </c>
+      <c r="B159">
+        <v>2021</v>
+      </c>
+      <c r="C159" t="s">
+        <v>69</v>
+      </c>
+      <c r="D159">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>34</v>
+      </c>
+      <c r="B160">
+        <v>2022</v>
+      </c>
+      <c r="C160" t="s">
+        <v>69</v>
+      </c>
+      <c r="D160">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>34</v>
+      </c>
+      <c r="B161">
+        <v>2023</v>
+      </c>
+      <c r="C161" t="s">
+        <v>69</v>
+      </c>
+      <c r="D161">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>34</v>
+      </c>
+      <c r="B162">
+        <v>2024</v>
+      </c>
+      <c r="C162" t="s">
+        <v>69</v>
+      </c>
+      <c r="D162">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>34</v>
+      </c>
+      <c r="B163">
+        <v>2025</v>
+      </c>
+      <c r="C163" t="s">
+        <v>69</v>
+      </c>
+      <c r="D163">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>34</v>
+      </c>
+      <c r="B164">
+        <v>2020</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>34</v>
+      </c>
+      <c r="B165">
+        <v>2021</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>34</v>
+      </c>
+      <c r="B166">
+        <v>2022</v>
+      </c>
+      <c r="C166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D166">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>34</v>
+      </c>
+      <c r="B167">
+        <v>2023</v>
+      </c>
+      <c r="C167" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>34</v>
+      </c>
+      <c r="B168">
+        <v>2024</v>
+      </c>
+      <c r="C168" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>34</v>
+      </c>
+      <c r="B169">
+        <v>2025</v>
+      </c>
+      <c r="C169" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>25</v>
+      </c>
+      <c r="B170">
+        <v>2020</v>
+      </c>
+      <c r="C170" t="s">
+        <v>105</v>
+      </c>
+      <c r="D170">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>25</v>
+      </c>
+      <c r="B171">
+        <v>2021</v>
+      </c>
+      <c r="C171" t="s">
+        <v>105</v>
+      </c>
+      <c r="D171">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>25</v>
+      </c>
+      <c r="B172">
+        <v>2022</v>
+      </c>
+      <c r="C172" t="s">
+        <v>105</v>
+      </c>
+      <c r="D172">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>25</v>
+      </c>
+      <c r="B173">
+        <v>2023</v>
+      </c>
+      <c r="C173" t="s">
+        <v>105</v>
+      </c>
+      <c r="D173">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>25</v>
+      </c>
+      <c r="B174">
+        <v>2024</v>
+      </c>
+      <c r="C174" t="s">
+        <v>105</v>
+      </c>
+      <c r="D174">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>25</v>
+      </c>
+      <c r="B175">
+        <v>2025</v>
+      </c>
+      <c r="C175" t="s">
+        <v>105</v>
+      </c>
+      <c r="D175">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>25</v>
+      </c>
+      <c r="B176">
+        <v>2020</v>
+      </c>
+      <c r="C176" t="s">
+        <v>88</v>
+      </c>
+      <c r="D176">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>25</v>
+      </c>
+      <c r="B177">
+        <v>2021</v>
+      </c>
+      <c r="C177" t="s">
+        <v>88</v>
+      </c>
+      <c r="D177">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>25</v>
+      </c>
+      <c r="B178">
+        <v>2022</v>
+      </c>
+      <c r="C178" t="s">
+        <v>88</v>
+      </c>
+      <c r="D178">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>25</v>
+      </c>
+      <c r="B179">
+        <v>2023</v>
+      </c>
+      <c r="C179" t="s">
+        <v>88</v>
+      </c>
+      <c r="D179">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>25</v>
+      </c>
+      <c r="B180">
+        <v>2024</v>
+      </c>
+      <c r="C180" t="s">
+        <v>88</v>
+      </c>
+      <c r="D180">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>25</v>
+      </c>
+      <c r="B181">
+        <v>2025</v>
+      </c>
+      <c r="C181" t="s">
+        <v>88</v>
+      </c>
+      <c r="D181">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>25</v>
+      </c>
+      <c r="B182">
+        <v>2020</v>
+      </c>
+      <c r="C182" t="s">
+        <v>102</v>
+      </c>
+      <c r="D182">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>25</v>
+      </c>
+      <c r="B183">
+        <v>2021</v>
+      </c>
+      <c r="C183" t="s">
+        <v>102</v>
+      </c>
+      <c r="D183">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>25</v>
+      </c>
+      <c r="B184">
+        <v>2022</v>
+      </c>
+      <c r="C184" t="s">
+        <v>102</v>
+      </c>
+      <c r="D184">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>25</v>
+      </c>
+      <c r="B185">
+        <v>2023</v>
+      </c>
+      <c r="C185" t="s">
+        <v>102</v>
+      </c>
+      <c r="D185">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>25</v>
+      </c>
+      <c r="B186">
+        <v>2024</v>
+      </c>
+      <c r="C186" t="s">
+        <v>102</v>
+      </c>
+      <c r="D186">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>25</v>
+      </c>
+      <c r="B187">
+        <v>2025</v>
+      </c>
+      <c r="C187" t="s">
+        <v>102</v>
+      </c>
+      <c r="D187">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>25</v>
+      </c>
+      <c r="B188">
+        <v>2020</v>
+      </c>
+      <c r="C188" t="s">
+        <v>60</v>
+      </c>
+      <c r="D188">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>25</v>
+      </c>
+      <c r="B189">
+        <v>2021</v>
+      </c>
+      <c r="C189" t="s">
+        <v>60</v>
+      </c>
+      <c r="D189">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>25</v>
+      </c>
+      <c r="B190">
+        <v>2022</v>
+      </c>
+      <c r="C190" t="s">
+        <v>60</v>
+      </c>
+      <c r="D190">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>25</v>
+      </c>
+      <c r="B191">
+        <v>2023</v>
+      </c>
+      <c r="C191" t="s">
+        <v>60</v>
+      </c>
+      <c r="D191">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>25</v>
+      </c>
+      <c r="B192">
+        <v>2024</v>
+      </c>
+      <c r="C192" t="s">
+        <v>60</v>
+      </c>
+      <c r="D192">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>25</v>
+      </c>
+      <c r="B193">
+        <v>2025</v>
+      </c>
+      <c r="C193" t="s">
+        <v>60</v>
+      </c>
+      <c r="D193">
+        <v>402</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{482657F8-43FC-45F9-9834-57F8F380F1AB}">
   <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/src/pages/data/data_corp_demo.xlsx
+++ b/src/pages/data/data_corp_demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/corporate_project/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="229" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F70375B-3FEA-4DF2-9DB2-8F90CB02B876}"/>
+  <xr:revisionPtr revIDLastSave="279" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D234B76-8FD9-4E37-8A51-E5A4E2113B82}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="3015" windowWidth="15375" windowHeight="7785" tabRatio="917" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="917" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_corp" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="115">
   <si>
     <t>UNIDAD_ACADEMICA</t>
   </si>
@@ -386,6 +386,12 @@
   </si>
   <si>
     <t>COLEGIO_REF</t>
+  </si>
+  <si>
+    <t>BÁSICA 1 y 2</t>
+  </si>
+  <si>
+    <t>PARV BÁSICA 1 y 2</t>
   </si>
 </sst>
 </file>
@@ -8086,10 +8092,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4E39ED-A2BA-4AF8-80FA-DB4BD0B334CE}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
@@ -8281,13 +8287,13 @@
         <v>2020</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="C14">
-        <v>1089</v>
+        <v>1393</v>
       </c>
       <c r="D14">
-        <v>7797</v>
+        <v>6389</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -8295,13 +8301,13 @@
         <v>2021</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="C15">
-        <v>1075</v>
+        <v>1404</v>
       </c>
       <c r="D15">
-        <v>7900</v>
+        <v>6434</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -8309,13 +8315,13 @@
         <v>2022</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="C16">
-        <v>1031</v>
+        <v>1381</v>
       </c>
       <c r="D16">
-        <v>7987</v>
+        <v>6582</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -8323,13 +8329,13 @@
         <v>2023</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="C17">
-        <v>989</v>
+        <v>1259</v>
       </c>
       <c r="D17">
-        <v>7929</v>
+        <v>6465</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -8337,13 +8343,13 @@
         <v>2024</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="C18">
-        <v>937</v>
+        <v>1159</v>
       </c>
       <c r="D18">
-        <v>7763</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -8351,13 +8357,13 @@
         <v>2025</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="C19">
-        <v>906</v>
+        <v>1119</v>
       </c>
       <c r="D19">
-        <v>7720</v>
+        <v>6074</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -8365,13 +8371,13 @@
         <v>2020</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20">
-        <v>129</v>
+        <v>1089</v>
       </c>
       <c r="D20">
-        <v>1346</v>
+        <v>7797</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -8379,13 +8385,13 @@
         <v>2021</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21">
-        <v>96</v>
+        <v>1075</v>
       </c>
       <c r="D21">
-        <v>1214</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -8393,13 +8399,13 @@
         <v>2022</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22">
-        <v>93</v>
+        <v>1031</v>
       </c>
       <c r="D22">
-        <v>1100</v>
+        <v>7987</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -8407,13 +8413,13 @@
         <v>2023</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
-        <v>67</v>
+        <v>989</v>
       </c>
       <c r="D23">
-        <v>1009</v>
+        <v>7929</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -8421,13 +8427,13 @@
         <v>2024</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24">
-        <v>57</v>
+        <v>937</v>
       </c>
       <c r="D24">
-        <v>930</v>
+        <v>7763</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -8435,13 +8441,13 @@
         <v>2025</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25">
-        <v>69</v>
+        <v>906</v>
       </c>
       <c r="D25">
-        <v>837</v>
+        <v>7720</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -8449,10 +8455,10 @@
         <v>2020</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D26">
         <v>1346</v>
@@ -8463,10 +8469,10 @@
         <v>2021</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D27">
         <v>1214</v>
@@ -8477,10 +8483,10 @@
         <v>2022</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C28">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D28">
         <v>1100</v>
@@ -8491,10 +8497,10 @@
         <v>2023</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D29">
         <v>1009</v>
@@ -8505,10 +8511,10 @@
         <v>2024</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="D30">
         <v>930</v>
@@ -8519,10 +8525,10 @@
         <v>2025</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C31">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D31">
         <v>837</v>
@@ -8533,13 +8539,13 @@
         <v>2020</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32">
-        <v>216</v>
+        <v>119</v>
       </c>
       <c r="D32">
-        <v>1391</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -8547,13 +8553,13 @@
         <v>2021</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33">
-        <v>170</v>
+        <v>101</v>
       </c>
       <c r="D33">
-        <v>1239</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -8561,13 +8567,13 @@
         <v>2022</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="D34">
-        <v>1237</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -8575,13 +8581,13 @@
         <v>2023</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C35">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="D35">
-        <v>1178</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -8589,13 +8595,13 @@
         <v>2024</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C36">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="D36">
-        <v>1108</v>
+        <v>930</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -8603,23 +8609,192 @@
         <v>2025</v>
       </c>
       <c r="B37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37">
+        <v>85</v>
+      </c>
+      <c r="D37">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2020</v>
+      </c>
+      <c r="B38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C38">
+        <v>248</v>
+      </c>
+      <c r="D38">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>2021</v>
+      </c>
+      <c r="B39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39">
+        <v>197</v>
+      </c>
+      <c r="D39">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2022</v>
+      </c>
+      <c r="B40" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40">
+        <v>188</v>
+      </c>
+      <c r="D40">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>2023</v>
+      </c>
+      <c r="B41" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41">
+        <v>137</v>
+      </c>
+      <c r="D41">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>2024</v>
+      </c>
+      <c r="B42" t="s">
+        <v>114</v>
+      </c>
+      <c r="C42">
+        <v>138</v>
+      </c>
+      <c r="D42">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>2025</v>
+      </c>
+      <c r="B43" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43">
+        <v>154</v>
+      </c>
+      <c r="D43">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>2020</v>
+      </c>
+      <c r="B44" t="s">
         <v>34</v>
       </c>
-      <c r="C37">
+      <c r="C44">
+        <v>216</v>
+      </c>
+      <c r="D44">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>2021</v>
+      </c>
+      <c r="B45" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45">
+        <v>170</v>
+      </c>
+      <c r="D45">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2022</v>
+      </c>
+      <c r="B46" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46">
+        <v>130</v>
+      </c>
+      <c r="D46">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>2023</v>
+      </c>
+      <c r="B47" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47">
+        <v>124</v>
+      </c>
+      <c r="D47">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>2024</v>
+      </c>
+      <c r="B48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48">
+        <v>111</v>
+      </c>
+      <c r="D48">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>2025</v>
+      </c>
+      <c r="B49" t="s">
+        <v>34</v>
+      </c>
+      <c r="C49">
         <v>89</v>
       </c>
-      <c r="D37">
+      <c r="D49">
         <v>1052</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3559129D-134A-4AB2-A379-E6F6068EBE81}">
-  <dimension ref="A1:B138"/>
+  <dimension ref="A1:B176"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
@@ -8956,162 +9131,162 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B45" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B51" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B60" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B61" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -9119,7 +9294,7 @@
         <v>31</v>
       </c>
       <c r="B62" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -9127,7 +9302,7 @@
         <v>31</v>
       </c>
       <c r="B63" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -9135,7 +9310,7 @@
         <v>31</v>
       </c>
       <c r="B64" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -9143,7 +9318,7 @@
         <v>31</v>
       </c>
       <c r="B65" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -9151,7 +9326,7 @@
         <v>31</v>
       </c>
       <c r="B66" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -9159,7 +9334,7 @@
         <v>31</v>
       </c>
       <c r="B67" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -9167,7 +9342,7 @@
         <v>31</v>
       </c>
       <c r="B68" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -9175,7 +9350,7 @@
         <v>31</v>
       </c>
       <c r="B69" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -9183,7 +9358,7 @@
         <v>31</v>
       </c>
       <c r="B70" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -9191,7 +9366,7 @@
         <v>31</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -9199,538 +9374,843 @@
         <v>31</v>
       </c>
       <c r="B72" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B73" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B74" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B75" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B76" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B77" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B78" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B79" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B80" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B81" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B82" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B83" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B84" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B85" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B86" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B87" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B88" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B89" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B90" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B91" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B92" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B93" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B94" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B95" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B96" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B97" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B99" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B100" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B101" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B102" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B103" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B104" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B105" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B106" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B107" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B108" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B109" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B110" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B111" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B112" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B113" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B114" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B115" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B116" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B117" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B118" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B119" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B120" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B121" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B122" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B123" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B124" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B125" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B126" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B127" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B128" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="B129" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="B130" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="B131" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="B132" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="B133" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="B134" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="B135" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="B136" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="B137" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>114</v>
+      </c>
+      <c r="B138" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>114</v>
+      </c>
+      <c r="B139" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>114</v>
+      </c>
+      <c r="B140" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>114</v>
+      </c>
+      <c r="B141" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>114</v>
+      </c>
+      <c r="B142" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>114</v>
+      </c>
+      <c r="B143" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>114</v>
+      </c>
+      <c r="B144" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>114</v>
+      </c>
+      <c r="B145" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>114</v>
+      </c>
+      <c r="B146" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
         <v>34</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B147" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>34</v>
+      </c>
+      <c r="B148" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>34</v>
+      </c>
+      <c r="B149" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>34</v>
+      </c>
+      <c r="B150" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>34</v>
+      </c>
+      <c r="B151" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>34</v>
+      </c>
+      <c r="B152" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>34</v>
+      </c>
+      <c r="B153" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>34</v>
+      </c>
+      <c r="B154" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>34</v>
+      </c>
+      <c r="B155" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>34</v>
+      </c>
+      <c r="B156" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>34</v>
+      </c>
+      <c r="B157" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>34</v>
+      </c>
+      <c r="B158" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>34</v>
+      </c>
+      <c r="B159" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>34</v>
+      </c>
+      <c r="B160" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>34</v>
+      </c>
+      <c r="B161" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>34</v>
+      </c>
+      <c r="B162" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>34</v>
+      </c>
+      <c r="B163" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>34</v>
+      </c>
+      <c r="B164" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>34</v>
+      </c>
+      <c r="B165" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>34</v>
+      </c>
+      <c r="B166" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>34</v>
+      </c>
+      <c r="B167" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>34</v>
+      </c>
+      <c r="B168" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>34</v>
+      </c>
+      <c r="B169" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>34</v>
+      </c>
+      <c r="B170" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>34</v>
+      </c>
+      <c r="B171" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>34</v>
+      </c>
+      <c r="B172" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>34</v>
+      </c>
+      <c r="B173" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>34</v>
+      </c>
+      <c r="B174" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>34</v>
+      </c>
+      <c r="B175" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>34</v>
+      </c>
+      <c r="B176" t="s">
         <v>90</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9850,7 +10330,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{698C1C06-077D-4280-80CF-7D6AE0F9E340}">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D241"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
@@ -10883,679 +11363,679 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B74">
         <v>2020</v>
       </c>
       <c r="C74" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D74">
-        <v>207</v>
+        <v>821</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B75">
         <v>2021</v>
       </c>
       <c r="C75" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D75">
-        <v>202</v>
+        <v>874</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B76">
         <v>2022</v>
       </c>
       <c r="C76" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D76">
-        <v>187</v>
+        <v>898</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B77">
         <v>2023</v>
       </c>
       <c r="C77" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D77">
-        <v>178</v>
+        <v>846</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B78">
         <v>2024</v>
       </c>
       <c r="C78" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D78">
-        <v>172</v>
+        <v>802</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B79">
         <v>2025</v>
       </c>
       <c r="C79" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D79">
-        <v>171</v>
+        <v>749</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B80">
         <v>2020</v>
       </c>
       <c r="C80" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D80">
-        <v>983</v>
+        <v>221</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B81">
         <v>2021</v>
       </c>
       <c r="C81" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D81">
-        <v>1005</v>
+        <v>225</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B82">
         <v>2022</v>
       </c>
       <c r="C82" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D82">
-        <v>929</v>
+        <v>228</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B83">
         <v>2023</v>
       </c>
       <c r="C83" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D83">
-        <v>820</v>
+        <v>227</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B84">
         <v>2024</v>
       </c>
       <c r="C84" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D84">
-        <v>722</v>
+        <v>208</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B85">
         <v>2025</v>
       </c>
       <c r="C85" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D85">
-        <v>698</v>
+        <v>208</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B86">
         <v>2020</v>
       </c>
       <c r="C86" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D86">
-        <v>156</v>
+        <v>617</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B87">
         <v>2021</v>
       </c>
       <c r="C87" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D87">
-        <v>162</v>
+        <v>631</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B88">
         <v>2022</v>
       </c>
       <c r="C88" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D88">
-        <v>165</v>
+        <v>622</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B89">
         <v>2023</v>
       </c>
       <c r="C89" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D89">
-        <v>173</v>
+        <v>623</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B90">
         <v>2024</v>
       </c>
       <c r="C90" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D90">
-        <v>175</v>
+        <v>610</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B91">
         <v>2025</v>
       </c>
       <c r="C91" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D91">
-        <v>163</v>
+        <v>619</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B92">
         <v>2020</v>
       </c>
       <c r="C92" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D92">
-        <v>141</v>
+        <v>814</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B93">
         <v>2021</v>
       </c>
       <c r="C93" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D93">
-        <v>143</v>
+        <v>835</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B94">
         <v>2022</v>
       </c>
       <c r="C94" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D94">
-        <v>133</v>
+        <v>802</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B95">
         <v>2023</v>
       </c>
       <c r="C95" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D95">
-        <v>135</v>
+        <v>775</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B96">
         <v>2024</v>
       </c>
       <c r="C96" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D96">
-        <v>152</v>
+        <v>739</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B97">
         <v>2025</v>
       </c>
       <c r="C97" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D97">
-        <v>153</v>
+        <v>709</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B98">
         <v>2020</v>
       </c>
       <c r="C98" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="D98">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B99">
         <v>2021</v>
       </c>
       <c r="C99" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="D99">
-        <v>185</v>
+        <v>202</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B100">
         <v>2022</v>
       </c>
       <c r="C100" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="D100">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B101">
         <v>2023</v>
       </c>
       <c r="C101" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="D101">
-        <v>156</v>
+        <v>178</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B102">
         <v>2024</v>
       </c>
       <c r="C102" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="D102">
-        <v>153</v>
+        <v>172</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B103">
         <v>2025</v>
       </c>
       <c r="C103" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="D103">
-        <v>132</v>
+        <v>171</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B104">
         <v>2020</v>
       </c>
       <c r="C104" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D104">
-        <v>36</v>
+        <v>983</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B105">
         <v>2021</v>
       </c>
       <c r="C105" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D105">
-        <v>29</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B106">
         <v>2022</v>
       </c>
       <c r="C106" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D106">
-        <v>27</v>
+        <v>929</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B107">
         <v>2023</v>
       </c>
       <c r="C107" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D107">
-        <v>21</v>
+        <v>820</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B108">
         <v>2024</v>
       </c>
       <c r="C108" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D108">
-        <v>31</v>
+        <v>722</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B109">
         <v>2025</v>
       </c>
       <c r="C109" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D109">
-        <v>32</v>
+        <v>698</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B110">
         <v>2020</v>
       </c>
       <c r="C110" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="D110">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B111">
         <v>2021</v>
       </c>
       <c r="C111" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="D111">
-        <v>138</v>
+        <v>162</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B112">
         <v>2022</v>
       </c>
       <c r="C112" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="D112">
-        <v>130</v>
+        <v>165</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B113">
         <v>2023</v>
       </c>
       <c r="C113" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="D113">
-        <v>129</v>
+        <v>173</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B114">
         <v>2024</v>
       </c>
       <c r="C114" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="D114">
-        <v>116</v>
+        <v>175</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B115">
         <v>2025</v>
       </c>
       <c r="C115" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="D115">
-        <v>98</v>
+        <v>163</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B116">
         <v>2020</v>
       </c>
       <c r="C116" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D116">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B117">
         <v>2021</v>
       </c>
       <c r="C117" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D117">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B118">
         <v>2022</v>
       </c>
       <c r="C118" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D118">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B119">
         <v>2023</v>
       </c>
       <c r="C119" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D119">
-        <v>94</v>
+        <v>135</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B120">
         <v>2024</v>
       </c>
       <c r="C120" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D120">
-        <v>78</v>
+        <v>152</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B121">
         <v>2025</v>
       </c>
       <c r="C121" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D121">
-        <v>76</v>
+        <v>153</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B122">
         <v>2020</v>
@@ -11569,7 +12049,7 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B123">
         <v>2021</v>
@@ -11583,7 +12063,7 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B124">
         <v>2022</v>
@@ -11597,7 +12077,7 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B125">
         <v>2023</v>
@@ -11611,7 +12091,7 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B126">
         <v>2024</v>
@@ -11625,7 +12105,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B127">
         <v>2025</v>
@@ -11639,7 +12119,7 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B128">
         <v>2020</v>
@@ -11653,7 +12133,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B129">
         <v>2021</v>
@@ -11667,7 +12147,7 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B130">
         <v>2022</v>
@@ -11681,7 +12161,7 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B131">
         <v>2023</v>
@@ -11695,7 +12175,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B132">
         <v>2024</v>
@@ -11709,7 +12189,7 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B133">
         <v>2025</v>
@@ -11723,7 +12203,7 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B134">
         <v>2020</v>
@@ -11737,7 +12217,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B135">
         <v>2021</v>
@@ -11751,7 +12231,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B136">
         <v>2022</v>
@@ -11765,7 +12245,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B137">
         <v>2023</v>
@@ -11779,7 +12259,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B138">
         <v>2024</v>
@@ -11793,7 +12273,7 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B139">
         <v>2025</v>
@@ -11807,7 +12287,7 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B140">
         <v>2020</v>
@@ -11821,7 +12301,7 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B141">
         <v>2021</v>
@@ -11835,7 +12315,7 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B142">
         <v>2022</v>
@@ -11849,7 +12329,7 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B143">
         <v>2023</v>
@@ -11863,7 +12343,7 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B144">
         <v>2024</v>
@@ -11877,7 +12357,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B145">
         <v>2025</v>
@@ -11891,673 +12371,1345 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B146">
         <v>2020</v>
       </c>
       <c r="C146" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D146">
-        <v>40</v>
+        <v>212</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B147">
         <v>2021</v>
       </c>
       <c r="C147" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D147">
-        <v>31</v>
+        <v>185</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B148">
         <v>2022</v>
       </c>
       <c r="C148" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D148">
-        <v>24</v>
+        <v>171</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B149">
         <v>2023</v>
       </c>
       <c r="C149" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D149">
-        <v>20</v>
+        <v>156</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B150">
         <v>2024</v>
       </c>
       <c r="C150" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D150">
-        <v>34</v>
+        <v>153</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B151">
         <v>2025</v>
       </c>
       <c r="C151" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D151">
-        <v>28</v>
+        <v>132</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B152">
         <v>2020</v>
       </c>
       <c r="C152" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D152">
-        <v>127</v>
+        <v>36</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B153">
         <v>2021</v>
       </c>
       <c r="C153" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D153">
-        <v>101</v>
+        <v>29</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B154">
         <v>2022</v>
       </c>
       <c r="C154" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D154">
-        <v>105</v>
+        <v>27</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B155">
         <v>2023</v>
       </c>
       <c r="C155" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D155">
-        <v>84</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B156">
         <v>2024</v>
       </c>
       <c r="C156" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D156">
-        <v>77</v>
+        <v>31</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B157">
         <v>2025</v>
       </c>
       <c r="C157" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D157">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B158">
         <v>2020</v>
       </c>
       <c r="C158" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D158">
-        <v>24</v>
+        <v>150</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B159">
         <v>2021</v>
       </c>
       <c r="C159" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D159">
-        <v>22</v>
+        <v>138</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B160">
         <v>2022</v>
       </c>
       <c r="C160" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D160">
-        <v>25</v>
+        <v>130</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B161">
         <v>2023</v>
       </c>
       <c r="C161" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D161">
-        <v>30</v>
+        <v>129</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B162">
         <v>2024</v>
       </c>
       <c r="C162" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D162">
-        <v>26</v>
+        <v>116</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B163">
         <v>2025</v>
       </c>
       <c r="C163" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D163">
-        <v>27</v>
+        <v>98</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B164">
         <v>2020</v>
       </c>
       <c r="C164" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D164">
-        <v>22</v>
+        <v>149</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B165">
         <v>2021</v>
       </c>
       <c r="C165" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D165">
-        <v>18</v>
+        <v>145</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B166">
         <v>2022</v>
       </c>
       <c r="C166" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D166">
-        <v>17</v>
+        <v>119</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B167">
         <v>2023</v>
       </c>
       <c r="C167" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D167">
-        <v>19</v>
+        <v>94</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B168">
         <v>2024</v>
       </c>
       <c r="C168" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D168">
-        <v>20</v>
+        <v>78</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B169">
         <v>2025</v>
       </c>
       <c r="C169" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D169">
-        <v>22</v>
+        <v>76</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B170">
         <v>2020</v>
       </c>
       <c r="C170" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D170">
-        <v>1153</v>
+        <v>212</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B171">
         <v>2021</v>
       </c>
       <c r="C171" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D171">
-        <v>1198</v>
+        <v>185</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B172">
         <v>2022</v>
       </c>
       <c r="C172" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D172">
-        <v>1203</v>
+        <v>171</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B173">
         <v>2023</v>
       </c>
       <c r="C173" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D173">
-        <v>1157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B174">
         <v>2024</v>
       </c>
       <c r="C174" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D174">
-        <v>1149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B175">
         <v>2025</v>
       </c>
       <c r="C175" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D175">
-        <v>1189</v>
+        <v>132</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B176">
         <v>2020</v>
       </c>
       <c r="C176" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="D176">
-        <v>196</v>
+        <v>36</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B177">
         <v>2021</v>
       </c>
       <c r="C177" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="D177">
-        <v>188</v>
+        <v>29</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B178">
         <v>2022</v>
       </c>
       <c r="C178" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="D178">
-        <v>165</v>
+        <v>27</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B179">
         <v>2023</v>
       </c>
       <c r="C179" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="D179">
-        <v>205</v>
+        <v>21</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B180">
         <v>2024</v>
       </c>
       <c r="C180" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="D180">
-        <v>240</v>
+        <v>31</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B181">
         <v>2025</v>
       </c>
       <c r="C181" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="D181">
-        <v>266</v>
+        <v>32</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B182">
         <v>2020</v>
       </c>
       <c r="C182" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="D182">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B183">
         <v>2021</v>
       </c>
       <c r="C183" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="D183">
-        <v>220</v>
+        <v>138</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B184">
         <v>2022</v>
       </c>
       <c r="C184" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="D184">
-        <v>250</v>
+        <v>130</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B185">
         <v>2023</v>
       </c>
       <c r="C185" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="D185">
-        <v>324</v>
+        <v>129</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B186">
         <v>2024</v>
       </c>
       <c r="C186" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="D186">
-        <v>331</v>
+        <v>116</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B187">
         <v>2025</v>
       </c>
       <c r="C187" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="D187">
-        <v>327</v>
+        <v>98</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B188">
         <v>2020</v>
       </c>
       <c r="C188" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D188">
-        <v>376</v>
+        <v>149</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B189">
         <v>2021</v>
       </c>
       <c r="C189" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D189">
-        <v>394</v>
+        <v>145</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B190">
         <v>2022</v>
       </c>
       <c r="C190" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D190">
-        <v>387</v>
+        <v>119</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B191">
         <v>2023</v>
       </c>
       <c r="C191" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D191">
-        <v>379</v>
+        <v>94</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B192">
         <v>2024</v>
       </c>
       <c r="C192" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D192">
-        <v>403</v>
+        <v>78</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B193">
         <v>2025</v>
       </c>
       <c r="C193" t="s">
+        <v>59</v>
+      </c>
+      <c r="D193">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>34</v>
+      </c>
+      <c r="B194">
+        <v>2020</v>
+      </c>
+      <c r="C194" t="s">
+        <v>75</v>
+      </c>
+      <c r="D194">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>34</v>
+      </c>
+      <c r="B195">
+        <v>2021</v>
+      </c>
+      <c r="C195" t="s">
+        <v>75</v>
+      </c>
+      <c r="D195">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>34</v>
+      </c>
+      <c r="B196">
+        <v>2022</v>
+      </c>
+      <c r="C196" t="s">
+        <v>75</v>
+      </c>
+      <c r="D196">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>34</v>
+      </c>
+      <c r="B197">
+        <v>2023</v>
+      </c>
+      <c r="C197" t="s">
+        <v>75</v>
+      </c>
+      <c r="D197">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>34</v>
+      </c>
+      <c r="B198">
+        <v>2024</v>
+      </c>
+      <c r="C198" t="s">
+        <v>75</v>
+      </c>
+      <c r="D198">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>34</v>
+      </c>
+      <c r="B199">
+        <v>2025</v>
+      </c>
+      <c r="C199" t="s">
+        <v>75</v>
+      </c>
+      <c r="D199">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>34</v>
+      </c>
+      <c r="B200">
+        <v>2020</v>
+      </c>
+      <c r="C200" t="s">
+        <v>72</v>
+      </c>
+      <c r="D200">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>34</v>
+      </c>
+      <c r="B201">
+        <v>2021</v>
+      </c>
+      <c r="C201" t="s">
+        <v>72</v>
+      </c>
+      <c r="D201">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>34</v>
+      </c>
+      <c r="B202">
+        <v>2022</v>
+      </c>
+      <c r="C202" t="s">
+        <v>72</v>
+      </c>
+      <c r="D202">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>34</v>
+      </c>
+      <c r="B203">
+        <v>2023</v>
+      </c>
+      <c r="C203" t="s">
+        <v>72</v>
+      </c>
+      <c r="D203">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>34</v>
+      </c>
+      <c r="B204">
+        <v>2024</v>
+      </c>
+      <c r="C204" t="s">
+        <v>72</v>
+      </c>
+      <c r="D204">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>34</v>
+      </c>
+      <c r="B205">
+        <v>2025</v>
+      </c>
+      <c r="C205" t="s">
+        <v>72</v>
+      </c>
+      <c r="D205">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>34</v>
+      </c>
+      <c r="B206">
+        <v>2020</v>
+      </c>
+      <c r="C206" t="s">
+        <v>69</v>
+      </c>
+      <c r="D206">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>34</v>
+      </c>
+      <c r="B207">
+        <v>2021</v>
+      </c>
+      <c r="C207" t="s">
+        <v>69</v>
+      </c>
+      <c r="D207">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>34</v>
+      </c>
+      <c r="B208">
+        <v>2022</v>
+      </c>
+      <c r="C208" t="s">
+        <v>69</v>
+      </c>
+      <c r="D208">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>34</v>
+      </c>
+      <c r="B209">
+        <v>2023</v>
+      </c>
+      <c r="C209" t="s">
+        <v>69</v>
+      </c>
+      <c r="D209">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>34</v>
+      </c>
+      <c r="B210">
+        <v>2024</v>
+      </c>
+      <c r="C210" t="s">
+        <v>69</v>
+      </c>
+      <c r="D210">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>34</v>
+      </c>
+      <c r="B211">
+        <v>2025</v>
+      </c>
+      <c r="C211" t="s">
+        <v>69</v>
+      </c>
+      <c r="D211">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>34</v>
+      </c>
+      <c r="B212">
+        <v>2020</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>34</v>
+      </c>
+      <c r="B213">
+        <v>2021</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>34</v>
+      </c>
+      <c r="B214">
+        <v>2022</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>34</v>
+      </c>
+      <c r="B215">
+        <v>2023</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>34</v>
+      </c>
+      <c r="B216">
+        <v>2024</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>34</v>
+      </c>
+      <c r="B217">
+        <v>2025</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>25</v>
+      </c>
+      <c r="B218">
+        <v>2020</v>
+      </c>
+      <c r="C218" t="s">
+        <v>105</v>
+      </c>
+      <c r="D218">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>25</v>
+      </c>
+      <c r="B219">
+        <v>2021</v>
+      </c>
+      <c r="C219" t="s">
+        <v>105</v>
+      </c>
+      <c r="D219">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>25</v>
+      </c>
+      <c r="B220">
+        <v>2022</v>
+      </c>
+      <c r="C220" t="s">
+        <v>105</v>
+      </c>
+      <c r="D220">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>25</v>
+      </c>
+      <c r="B221">
+        <v>2023</v>
+      </c>
+      <c r="C221" t="s">
+        <v>105</v>
+      </c>
+      <c r="D221">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>25</v>
+      </c>
+      <c r="B222">
+        <v>2024</v>
+      </c>
+      <c r="C222" t="s">
+        <v>105</v>
+      </c>
+      <c r="D222">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>25</v>
+      </c>
+      <c r="B223">
+        <v>2025</v>
+      </c>
+      <c r="C223" t="s">
+        <v>105</v>
+      </c>
+      <c r="D223">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>25</v>
+      </c>
+      <c r="B224">
+        <v>2020</v>
+      </c>
+      <c r="C224" t="s">
+        <v>88</v>
+      </c>
+      <c r="D224">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>25</v>
+      </c>
+      <c r="B225">
+        <v>2021</v>
+      </c>
+      <c r="C225" t="s">
+        <v>88</v>
+      </c>
+      <c r="D225">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>25</v>
+      </c>
+      <c r="B226">
+        <v>2022</v>
+      </c>
+      <c r="C226" t="s">
+        <v>88</v>
+      </c>
+      <c r="D226">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>25</v>
+      </c>
+      <c r="B227">
+        <v>2023</v>
+      </c>
+      <c r="C227" t="s">
+        <v>88</v>
+      </c>
+      <c r="D227">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>25</v>
+      </c>
+      <c r="B228">
+        <v>2024</v>
+      </c>
+      <c r="C228" t="s">
+        <v>88</v>
+      </c>
+      <c r="D228">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>25</v>
+      </c>
+      <c r="B229">
+        <v>2025</v>
+      </c>
+      <c r="C229" t="s">
+        <v>88</v>
+      </c>
+      <c r="D229">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>25</v>
+      </c>
+      <c r="B230">
+        <v>2020</v>
+      </c>
+      <c r="C230" t="s">
+        <v>102</v>
+      </c>
+      <c r="D230">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>25</v>
+      </c>
+      <c r="B231">
+        <v>2021</v>
+      </c>
+      <c r="C231" t="s">
+        <v>102</v>
+      </c>
+      <c r="D231">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>25</v>
+      </c>
+      <c r="B232">
+        <v>2022</v>
+      </c>
+      <c r="C232" t="s">
+        <v>102</v>
+      </c>
+      <c r="D232">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>25</v>
+      </c>
+      <c r="B233">
+        <v>2023</v>
+      </c>
+      <c r="C233" t="s">
+        <v>102</v>
+      </c>
+      <c r="D233">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>25</v>
+      </c>
+      <c r="B234">
+        <v>2024</v>
+      </c>
+      <c r="C234" t="s">
+        <v>102</v>
+      </c>
+      <c r="D234">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>25</v>
+      </c>
+      <c r="B235">
+        <v>2025</v>
+      </c>
+      <c r="C235" t="s">
+        <v>102</v>
+      </c>
+      <c r="D235">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>25</v>
+      </c>
+      <c r="B236">
+        <v>2020</v>
+      </c>
+      <c r="C236" t="s">
         <v>60</v>
       </c>
-      <c r="D193">
+      <c r="D236">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>25</v>
+      </c>
+      <c r="B237">
+        <v>2021</v>
+      </c>
+      <c r="C237" t="s">
+        <v>60</v>
+      </c>
+      <c r="D237">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>25</v>
+      </c>
+      <c r="B238">
+        <v>2022</v>
+      </c>
+      <c r="C238" t="s">
+        <v>60</v>
+      </c>
+      <c r="D238">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>25</v>
+      </c>
+      <c r="B239">
+        <v>2023</v>
+      </c>
+      <c r="C239" t="s">
+        <v>60</v>
+      </c>
+      <c r="D239">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>25</v>
+      </c>
+      <c r="B240">
+        <v>2024</v>
+      </c>
+      <c r="C240" t="s">
+        <v>60</v>
+      </c>
+      <c r="D240">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>25</v>
+      </c>
+      <c r="B241">
+        <v>2025</v>
+      </c>
+      <c r="C241" t="s">
+        <v>60</v>
+      </c>
+      <c r="D241">
         <v>402</v>
       </c>
     </row>
